--- a/src/attributions/attributions_saliency_traj_468.xlsx
+++ b/src/attributions/attributions_saliency_traj_468.xlsx
@@ -999,1140 +999,1140 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02728123217821121</v>
+        <v>0.9287935495376587</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05292737483978271</v>
+        <v>2.779666900634766</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00270942784845829</v>
+        <v>0.5846407413482666</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01614947989583015</v>
+        <v>0.4757198095321655</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06876175105571747</v>
+        <v>1.109599590301514</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008935191668570042</v>
+        <v>0.2235846519470215</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01515139266848564</v>
+        <v>0.03775183856487274</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01816871576011181</v>
+        <v>0.2196918129920959</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008918492123484612</v>
+        <v>0.4540467262268066</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01718245819211006</v>
+        <v>0.6044259667396545</v>
       </c>
       <c r="K2" t="n">
-        <v>0.06307777762413025</v>
+        <v>3.773066997528076</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00400615343824029</v>
+        <v>0.6518098115921021</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03981141373515129</v>
+        <v>0.6172025799751282</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07700783014297485</v>
+        <v>1.276635885238647</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03024841472506523</v>
+        <v>0.4187825918197632</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01736246235668659</v>
+        <v>0.4573310017585754</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02665337361395359</v>
+        <v>0.6310707330703735</v>
       </c>
       <c r="R2" t="n">
-        <v>0.02609911933541298</v>
+        <v>0.7800966501235962</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003285155165940523</v>
+        <v>0.03542046993970871</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03519607335329056</v>
+        <v>0.2815924882888794</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01045514643192291</v>
+        <v>0.122856006026268</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01985084265470505</v>
+        <v>0.3720042407512665</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02350513637065887</v>
+        <v>0.004641078412532806</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03533106297254562</v>
+        <v>0.1499806046485901</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.02373902499675751</v>
+        <v>0.07841253280639648</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008524969220161438</v>
+        <v>0.1443440616130829</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004699861630797386</v>
+        <v>0.4365824162960052</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01870157010853291</v>
+        <v>0.1602338701486588</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.02335091680288315</v>
+        <v>0.3642687797546387</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0127959381788969</v>
+        <v>0.3289775848388672</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.003476683050394058</v>
+        <v>0.3758198618888855</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.01630956493318081</v>
+        <v>0.1046182587742805</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002539388835430145</v>
+        <v>0.2606188356876373</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0368584617972374</v>
+        <v>0.08548934757709503</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.01443025283515453</v>
+        <v>0.2165811657905579</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.004760148469358683</v>
+        <v>0.2114894688129425</v>
       </c>
       <c r="AK2" t="n">
-        <v>5.427107680588961e-05</v>
+        <v>0.04687117040157318</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.02369632013142109</v>
+        <v>0.7560232877731323</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0008354164310730994</v>
+        <v>0.1389340758323669</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.008390765637159348</v>
+        <v>0.1560554206371307</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.01392180752009153</v>
+        <v>0.3148489594459534</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.004512956365942955</v>
+        <v>0.1470634788274765</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.006300489418208599</v>
+        <v>0.27934929728508</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.01364338956773281</v>
+        <v>0.3324733078479767</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.007889607921242714</v>
+        <v>0.135932669043541</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.01992494240403175</v>
+        <v>0.2142756581306458</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.03232990950345993</v>
+        <v>2.544193983078003</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.832605817588046e-05</v>
+        <v>0.3709984421730042</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.003956217784434557</v>
+        <v>0.1762049198150635</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.00118640623986721</v>
+        <v>0.461424857378006</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.005526697263121605</v>
+        <v>0.01116441562771797</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.01338255405426025</v>
+        <v>0.03065386787056923</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.007085570134222507</v>
+        <v>0.4913095235824585</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.01550361979752779</v>
+        <v>0.1160489097237587</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.007371705956757069</v>
+        <v>0.743711531162262</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.02127525210380554</v>
+        <v>0.08135448396205902</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.003789428388699889</v>
+        <v>0.6736358404159546</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.01702402532100677</v>
+        <v>0.370392769575119</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.07997909933328629</v>
+        <v>0.4135450720787048</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.0004765861667692661</v>
+        <v>0.4220505058765411</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.00933600589632988</v>
+        <v>0.3233901262283325</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.01683029904961586</v>
+        <v>0.1924222707748413</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.02310116402804852</v>
+        <v>0.06910577416419983</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.005632809363305569</v>
+        <v>0.08342958986759186</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.03583559021353722</v>
+        <v>0.09893502295017242</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.009350042790174484</v>
+        <v>0.1030519753694534</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.01280212588608265</v>
+        <v>0.1674278974533081</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.01454748213291168</v>
+        <v>0.6580895185470581</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.01226490922272205</v>
+        <v>0.04863495007157326</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.002034036908298731</v>
+        <v>0.5397986173629761</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.0003027035854756832</v>
+        <v>0.1055171564221382</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.0152974771335721</v>
+        <v>0.2590112090110779</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.009708289057016373</v>
+        <v>0.1259277313947678</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.03105758316814899</v>
+        <v>1.608465552330017</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.002176630776375532</v>
+        <v>0.07807046175003052</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.009894076734781265</v>
+        <v>0.3952119052410126</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.005492883268743753</v>
+        <v>0.2523938715457916</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.005095189437270164</v>
+        <v>0.03141900897026062</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.001779620768502355</v>
+        <v>0.3400168418884277</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.0008995572570711374</v>
+        <v>0.190712571144104</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.003065802622586489</v>
+        <v>0.3575760126113892</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.003965415991842747</v>
+        <v>0.1411293298006058</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.01289578247815371</v>
+        <v>1.016863703727722</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.003805872518569231</v>
+        <v>0.2139515280723572</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.00473040621727705</v>
+        <v>0.1080290451645851</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.00381022272631526</v>
+        <v>0.1732341349124908</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.002504845149815083</v>
+        <v>0.1997741013765335</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.009733718819916248</v>
+        <v>0.01975303515791893</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.002072286792099476</v>
+        <v>0.1034448742866516</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.001750331372022629</v>
+        <v>0.1602012664079666</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.02061657607555389</v>
+        <v>0.1669827252626419</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.005683038383722305</v>
+        <v>1.994428396224976</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.005369001533836126</v>
+        <v>0.3060662150382996</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.02425676211714745</v>
+        <v>0.1696185767650604</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.003215073607861996</v>
+        <v>0.1444220691919327</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.01850790344178677</v>
+        <v>0.2953870892524719</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.005354730878025293</v>
+        <v>0.2760183215141296</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.01230189204216003</v>
+        <v>0.3363193869590759</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.004878228530287743</v>
+        <v>0.0305364578962326</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.004105339758098125</v>
+        <v>0.0659017413854599</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.01648850739002228</v>
+        <v>1.014759540557861</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.0005964902811683714</v>
+        <v>0.1836258769035339</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.007678302470594645</v>
+        <v>0.02755994349718094</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.00454347999766469</v>
+        <v>0.01463230140507221</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0068850452080369</v>
+        <v>0.1262179762125015</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.009290998801589012</v>
+        <v>0.03716553375124931</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.006539877038449049</v>
+        <v>0.09743671119213104</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.005822049453854561</v>
+        <v>0.2570565640926361</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.006547318305820227</v>
+        <v>0.1275788843631744</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.01252224203199148</v>
+        <v>0.9569203853607178</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.01324420049786568</v>
+        <v>0.4528738558292389</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.02967347018420696</v>
+        <v>0.1333726048469543</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.02833870053291321</v>
+        <v>0.007961157709360123</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.03363540396094322</v>
+        <v>0.2866241335868835</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.007904013618826866</v>
+        <v>0.06610043346881866</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.02580998092889786</v>
+        <v>0.1290588676929474</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.02954641729593277</v>
+        <v>0.004556864500045776</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.0004096261691302061</v>
+        <v>0.0222541019320488</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.005729722790420055</v>
+        <v>0.5184997916221619</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.005701121874153614</v>
+        <v>0.1625228375196457</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.02355189993977547</v>
+        <v>0.1551537364721298</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.005738303996622562</v>
+        <v>0.2262172847986221</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.00819380022585392</v>
+        <v>0.226387232542038</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.03917632251977921</v>
+        <v>0.03407110646367073</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.001580301905050874</v>
+        <v>0.4524969458580017</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.003866434097290039</v>
+        <v>0.4505986571311951</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.00635960791260004</v>
+        <v>0.4726038873195648</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.01885049603879452</v>
+        <v>0.8009694814682007</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.01771869696676731</v>
+        <v>0.04589217528700829</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.002561939414590597</v>
+        <v>0.01207941770553589</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.01041063480079174</v>
+        <v>0.008106671273708344</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.001617651432752609</v>
+        <v>0.598875105381012</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.00257273274473846</v>
+        <v>0.1832840591669083</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.007892763242125511</v>
+        <v>0.4733977019786835</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.02101670950651169</v>
+        <v>0.3867586255073547</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.00566131342202425</v>
+        <v>0.06481665372848511</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.007304520811885595</v>
+        <v>0.6863099336624146</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.002722377888858318</v>
+        <v>0.1166543215513229</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.007731129880994558</v>
+        <v>0.1517773866653442</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.008061399683356285</v>
+        <v>0.01368877850472927</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.01071250811219215</v>
+        <v>0.3281593322753906</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.002937662415206432</v>
+        <v>0.004424517974257469</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.005945771001279354</v>
+        <v>0.03188306838274002</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.004774586297571659</v>
+        <v>0.1748926341533661</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.001289918320253491</v>
+        <v>0.06107416749000549</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.01858931221067905</v>
+        <v>0.3276702165603638</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.007271844893693924</v>
+        <v>0.07053346186876297</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.0006919836159795523</v>
+        <v>0.2167685478925705</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.01618674024939537</v>
+        <v>0.00177063001319766</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.004461583215743303</v>
+        <v>0.06650060415267944</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.004835186060518026</v>
+        <v>0.1546741724014282</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.01225804630666971</v>
+        <v>0.1846464276313782</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.003134846687316895</v>
+        <v>0.005562519654631615</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.003548286389559507</v>
+        <v>0.1217653602361679</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.01616748981177807</v>
+        <v>1.188943028450012</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.001255679642781615</v>
+        <v>0.1841247528791428</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.00936303474009037</v>
+        <v>0.03700301796197891</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.001640736940316856</v>
+        <v>0.003104281378909945</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.003878952469676733</v>
+        <v>0.122765801846981</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.004902004264295101</v>
+        <v>0.03765236213803291</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.005041709169745445</v>
+        <v>0.01091755554080009</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.003353502135723829</v>
+        <v>0.2838261127471924</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.01001804415136576</v>
+        <v>0.08913740515708923</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.00752198975533247</v>
+        <v>0.4308812022209167</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.01928141340613365</v>
+        <v>0.3580696284770966</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.01784499175846577</v>
+        <v>0.2753551006317139</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.003625981975346804</v>
+        <v>0.3928777873516083</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.00409228540956974</v>
+        <v>0.2899239063262939</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.02815824002027512</v>
+        <v>0.2688259780406952</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.008366554975509644</v>
+        <v>0.004241809248924255</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.007817191071808338</v>
+        <v>0.4856384992599487</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.01708119176328182</v>
+        <v>0.2229290902614594</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.04617972671985626</v>
+        <v>0.3904247879981995</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.01264153141528368</v>
+        <v>0.2223854809999466</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.03124539367854595</v>
+        <v>0.2170519828796387</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.001220246776938438</v>
+        <v>1.102451086044312</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.01201597601175308</v>
+        <v>0.08893951028585434</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.007294058799743652</v>
+        <v>0.2243538945913315</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.02887932956218719</v>
+        <v>0.5793206095695496</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.003076403401792049</v>
+        <v>0.4976208508014679</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.01783011853694916</v>
+        <v>0.1701762974262238</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.005734020844101906</v>
+        <v>0.774501621723175</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.009903518483042717</v>
+        <v>0.2332493215799332</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.003489155555143952</v>
+        <v>0.08249033242464066</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.03301798924803734</v>
+        <v>0.3317912518978119</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.008235392160713673</v>
+        <v>0.08380486071109772</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.04582986235618591</v>
+        <v>0.2718905806541443</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.00381687143817544</v>
+        <v>0.4383061826229095</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.01340189017355442</v>
+        <v>0.200710728764534</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.002665904350578785</v>
+        <v>0.02646474540233612</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02935645170509815</v>
+        <v>0.1366405934095383</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001537834294140339</v>
+        <v>0.01855657994747162</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03487084805965424</v>
+        <v>0.01533567253500223</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01506888400763273</v>
+        <v>0.03536127135157585</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02187651395797729</v>
+        <v>0.003435258753597736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02780991420149803</v>
+        <v>0.07246538996696472</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0146137960255146</v>
+        <v>0.03366770222783089</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01119567640125751</v>
+        <v>0.0172144528478384</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006395447999238968</v>
+        <v>0.01767453365027905</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03622597455978394</v>
+        <v>0.1417070627212524</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001414974918588996</v>
+        <v>0.02985173836350441</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04119071736931801</v>
+        <v>0.03757008910179138</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02256612665951252</v>
+        <v>0.009571571834385395</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0223897323012352</v>
+        <v>0.02887744829058647</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02184735611081123</v>
+        <v>0.1053224354982376</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001442618668079376</v>
+        <v>0.02810543775558472</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0226665772497654</v>
+        <v>0.06248521059751511</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001931686187162995</v>
+        <v>0.01962031051516533</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004426997154951096</v>
+        <v>0.002680623438209295</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001616247813217342</v>
+        <v>0.007026179693639278</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007735856343060732</v>
+        <v>0.03298808634281158</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009058023802936077</v>
+        <v>0.0132856760174036</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0005374987376853824</v>
+        <v>0.008329096250236034</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005651221144944429</v>
+        <v>0.03675547614693642</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0014284981880337</v>
+        <v>0.01653033681213856</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003546751569956541</v>
+        <v>0.01009480934590101</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.008944613859057426</v>
+        <v>0.005665692035108805</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.00599433109164238</v>
+        <v>0.01335958205163479</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.002318223705515265</v>
+        <v>0.002367482520639896</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.01756533049046993</v>
+        <v>0.00735781341791153</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.001398782478645444</v>
+        <v>0.001329045742750168</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.001691959099844098</v>
+        <v>0.009973411448299885</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.002855577971786261</v>
+        <v>0.01420027017593384</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0004070134600624442</v>
+        <v>0.01240435987710953</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.01151947677135468</v>
+        <v>0.0004063262604176998</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.003400040557608008</v>
+        <v>0.003741320222616196</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01043232344090939</v>
+        <v>0.03045012056827545</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.004475913010537624</v>
+        <v>0.001604163669981062</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.371150422841311e-05</v>
+        <v>0.04689722880721092</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.009999052621424198</v>
+        <v>0.04673680663108826</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.01004606392234564</v>
+        <v>0.009889354929327965</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.002229652600362897</v>
+        <v>0.04126228392124176</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.004268787801265717</v>
+        <v>0.007011658512055874</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.004613307304680347</v>
+        <v>0.01021648570895195</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.007179385516792536</v>
+        <v>0.001504211453720927</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.01713292300701141</v>
+        <v>0.05777610093355179</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.005707862786948681</v>
+        <v>0.009412313811480999</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.008422553539276123</v>
+        <v>0.04773294925689697</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.004644046537578106</v>
+        <v>0.01919941604137421</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.01036821119487286</v>
+        <v>0.0137247908860445</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.02210460975766182</v>
+        <v>0.0006243422394618392</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.001091819256544113</v>
+        <v>0.03113322518765926</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.00730760395526886</v>
+        <v>6.584031507372856e-05</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.005476891994476318</v>
+        <v>0.008643252775073051</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0005266843363642693</v>
+        <v>0.03794450312852859</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.006293586455285549</v>
+        <v>0.004842816852033138</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.009674025699496269</v>
+        <v>0.001854665577411652</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.001012310152873397</v>
+        <v>0.03808621317148209</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.01078712660819292</v>
+        <v>0.00264200521633029</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.006709921639412642</v>
+        <v>0.04520837590098381</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.001143158995546401</v>
+        <v>0.02033097110688686</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.01143962983042002</v>
+        <v>0.007013156544417143</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.000550250755622983</v>
+        <v>0.003726225811988115</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.01413967646658421</v>
+        <v>0.0309596098959446</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.003298805095255375</v>
+        <v>0.004719885997474194</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.00322423642501235</v>
+        <v>0.05027107521891594</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.006284172646701336</v>
+        <v>0.01373651530593634</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.004324056673794985</v>
+        <v>0.003489512018859386</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.007787774316966534</v>
+        <v>0.01980536617338657</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.001773488009348512</v>
+        <v>0.01024582888931036</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.001361443195492029</v>
+        <v>0.001567645347677171</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.005879619158804417</v>
+        <v>0.007325218059122562</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.01826290041208267</v>
+        <v>0.04119397699832916</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.002891656011343002</v>
+        <v>0.002106551546603441</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.001443179091438651</v>
+        <v>0.05218857154250145</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.009349776431918144</v>
+        <v>0.03690515831112862</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.007054253946989775</v>
+        <v>0.01084433123469353</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.01211181841790676</v>
+        <v>4.436448216438293e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.00404339050874114</v>
+        <v>0.006418142002075911</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.007433563936501741</v>
+        <v>0.005348923616111279</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.004782268777489662</v>
+        <v>0.007557692006230354</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.003249729750677943</v>
+        <v>0.03514391183853149</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.003027821658179164</v>
+        <v>0.005736317485570908</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.008014506660401821</v>
+        <v>0.04117896407842636</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.003473649034276605</v>
+        <v>0.006661639548838139</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.002444804180413485</v>
+        <v>0.009872499853372574</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.00696350634098053</v>
+        <v>0.02207003906369209</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.002237109234556556</v>
+        <v>0.009926103986799717</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.002273736987262964</v>
+        <v>0.00351428147405386</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.001000259770080447</v>
+        <v>0.02451385743916035</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.004076855257153511</v>
+        <v>0.04199374839663506</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.004530529957264662</v>
+        <v>0.004254159983247519</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.005401100032031536</v>
+        <v>0.007487159222364426</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.005144580733031034</v>
+        <v>0.04533711448311806</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.004219988826662302</v>
+        <v>0.02763541787862778</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.002168888226151466</v>
+        <v>0.01377085782587528</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.00315395649522543</v>
+        <v>0.01278455555438995</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.006014842074364424</v>
+        <v>0.01686400175094604</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.002671462250873446</v>
+        <v>0.005750657990574837</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.003297994844615459</v>
+        <v>0.03655632212758064</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.00426854845136404</v>
+        <v>0.005141892470419407</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.009508417919278145</v>
+        <v>0.03960209339857101</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.004104587249457836</v>
+        <v>0.002298922743648291</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.000822246540337801</v>
+        <v>0.009935647249221802</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.006406866014003754</v>
+        <v>0.0237573180347681</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.002695711562409997</v>
+        <v>0.006967912428081036</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.0008607443887740374</v>
+        <v>0.001892243511974812</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.002643232233822346</v>
+        <v>0.02015293762087822</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.0009746733121573925</v>
+        <v>0.005140522494912148</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.009260582737624645</v>
+        <v>0.001003901707008481</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.008047926239669323</v>
+        <v>0.02634510211646557</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.002654059091582894</v>
+        <v>0.01287413761019707</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.004174413159489632</v>
+        <v>0.04391947388648987</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.002594273537397385</v>
+        <v>0.02861183881759644</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.003280135104432702</v>
+        <v>0.00120629440061748</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.004925243090838194</v>
+        <v>0.01349938847124577</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.00675683468580246</v>
+        <v>0.00542531767860055</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.007619886659085751</v>
+        <v>0.02268903329968452</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.01159065961837769</v>
+        <v>0.01713367737829685</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.005026889033615589</v>
+        <v>0.02465841732919216</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.004942622501403093</v>
+        <v>0.002885080175474286</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.002821148606017232</v>
+        <v>0.01695743016898632</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.005902904085814953</v>
+        <v>0.01519874110817909</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.003834889968857169</v>
+        <v>0.004842795897275209</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.005747279152274132</v>
+        <v>0.01434445474296808</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.008928381837904453</v>
+        <v>0.003217335091903806</v>
       </c>
       <c r="DX3" t="n">
-        <v>5.57146267965436e-05</v>
+        <v>0.03895865008234978</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.007950304076075554</v>
+        <v>0.007721723522990942</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0008794150780886412</v>
+        <v>0.02783904410898685</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0020603914745152</v>
+        <v>0.05196265503764153</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.01380274724215269</v>
+        <v>0.001444597146473825</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.00301043875515461</v>
+        <v>0.0215569194406271</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.001981639303267002</v>
+        <v>0.02169622108340263</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.00610794685781002</v>
+        <v>0.03796067088842392</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.004724047146737576</v>
+        <v>0.0112029779702425</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.002390905283391476</v>
+        <v>0.02066772989928722</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.003637547139078379</v>
+        <v>0.003958716988563538</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.003016563132405281</v>
+        <v>0.05925440043210983</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.001903844648040831</v>
+        <v>0.0002398556098341942</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.002551582874730229</v>
+        <v>0.00670043146237731</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.00659831753000617</v>
+        <v>0.03023817203938961</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.0008066099835559726</v>
+        <v>0.006162042729556561</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.002328329021111131</v>
+        <v>0.004851553589105606</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.001216232310980558</v>
+        <v>0.006452459841966629</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.001901164301671088</v>
+        <v>0.02117987722158432</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.01211175415664911</v>
+        <v>0.00280458782799542</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.01332606002688408</v>
+        <v>0.02754674851894379</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.005371930077672005</v>
+        <v>0.01936968229711056</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.003272323170676827</v>
+        <v>0.01153933443129063</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.006508416496217251</v>
+        <v>0.001670034136623144</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.007352374959737062</v>
+        <v>0.02306210994720459</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.006117749027907848</v>
+        <v>0.004536057822406292</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.003490661270916462</v>
+        <v>0.008162614889442921</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.004597953055053949</v>
+        <v>0.03562112152576447</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.00339619955047965</v>
+        <v>0.005504419095814228</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.00851750373840332</v>
+        <v>0.03257603570818901</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.006433451548218727</v>
+        <v>0.007375219836831093</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.001978982705622911</v>
+        <v>0.00779236014932394</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.009574392810463905</v>
+        <v>0.01761506497859955</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.002704339800402522</v>
+        <v>0.0003116488223895431</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.001591298612765968</v>
+        <v>0.00329136336222291</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.001292714849114418</v>
+        <v>0.003123750444501638</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.003067229641601443</v>
+        <v>0.01023814082145691</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.005265702493488789</v>
+        <v>0.006873202510178089</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.0001860584015958011</v>
+        <v>0.03142523765563965</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.002014980185776949</v>
+        <v>0.0308520719408989</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.008131427690386772</v>
+        <v>0.01076162606477737</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.003157346975058317</v>
+        <v>0.005578985437750816</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.00206777872517705</v>
+        <v>0.05007335171103477</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.0008326470851898193</v>
+        <v>0.04367509111762047</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.0123115535825491</v>
+        <v>0.0485524982213974</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.01774612255394459</v>
+        <v>0.03406742215156555</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.005072387866675854</v>
+        <v>0.005056341178715229</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.01407961081713438</v>
+        <v>0.004569533281028271</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.01586971618235111</v>
+        <v>0.08733603358268738</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.006624380126595497</v>
+        <v>0.007974144071340561</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.01613039709627628</v>
+        <v>0.04828807711601257</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.01168545987457037</v>
+        <v>0.0624983124434948</v>
       </c>
       <c r="FX3" t="n">
-        <v>8.529407205060124e-05</v>
+        <v>0.01369382906705141</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.002179373055696487</v>
+        <v>0.0001488678390160203</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.002254146849736571</v>
+        <v>0.04123558849096298</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.006191933527588844</v>
+        <v>0.008642376400530338</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.003843103302642703</v>
+        <v>0.004421715158969164</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.0250385869294405</v>
+        <v>0.01610741950571537</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.009974139742553234</v>
+        <v>0.02321355976164341</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.01315033994615078</v>
+        <v>0.02664509601891041</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.007747868541628122</v>
+        <v>0.0004148196894675493</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.004784606862813234</v>
+        <v>0.005433897953480482</v>
       </c>
     </row>
     <row r="4">
@@ -2706,3985 +2706,3985 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.01403035968542099</v>
+        <v>0.04677002876996994</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2467246204614639</v>
+        <v>0.3136089444160461</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01562298089265823</v>
+        <v>0.02044606953859329</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1557034552097321</v>
+        <v>0.6767697334289551</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0079707195982337</v>
+        <v>0.03752105310559273</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05015110224485397</v>
+        <v>0.26042440533638</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0268733911216259</v>
+        <v>0.3685447871685028</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02530034817755222</v>
+        <v>0.27491095662117</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007852647453546524</v>
+        <v>0.0735468789935112</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0391245074570179</v>
+        <v>0.0590691864490509</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1836138218641281</v>
+        <v>0.2273970097303391</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0084207933396101</v>
+        <v>0.03877636045217514</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1365036815404892</v>
+        <v>0.9888970851898193</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03285062685608864</v>
+        <v>0.08193197101354599</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07643803954124451</v>
+        <v>0.3221252858638763</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01627182587981224</v>
+        <v>0.4200780987739563</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02253098972141743</v>
+        <v>0.02289320901036263</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01962447911500931</v>
+        <v>0.1106082275509834</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01228476874530315</v>
+        <v>0.01673437841236591</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02570417150855064</v>
+        <v>0.02506916411221027</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00143935636151582</v>
+        <v>0.04960963129997253</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03839802369475365</v>
+        <v>0.1435975432395935</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03089651092886925</v>
+        <v>0.1956259906291962</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01619298011064529</v>
+        <v>0.1397807747125626</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0235334038734436</v>
+        <v>0.003964979201555252</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03361133858561516</v>
+        <v>0.0444314181804657</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02888674288988113</v>
+        <v>0.04115996509790421</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009707417339086533</v>
+        <v>0.02614785358309746</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.02996840327978134</v>
+        <v>0.09407797455787659</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.01748479343950748</v>
+        <v>0.06275223195552826</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01219084206968546</v>
+        <v>0.04437355697154999</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.981216862797737e-06</v>
+        <v>0.08167524635791779</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.01555292028933764</v>
+        <v>0.1321655511856079</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.008479613810777664</v>
+        <v>0.09118182957172394</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.01154076121747494</v>
+        <v>0.1310649812221527</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.02257250435650349</v>
+        <v>0.1627899706363678</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.007744003552943468</v>
+        <v>0.04024598002433777</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.03304138407111168</v>
+        <v>0.1529540717601776</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.004157469142228365</v>
+        <v>0.08551087975502014</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.01201584562659264</v>
+        <v>0.1690402179956436</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.00776356179267168</v>
+        <v>0.03185012564063072</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.02426205575466156</v>
+        <v>0.1134042739868164</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.01029171235859394</v>
+        <v>0.1194390058517456</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.02246718853712082</v>
+        <v>0.09539700299501419</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.02201504446566105</v>
+        <v>0.04810759797692299</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.02136538922786713</v>
+        <v>0.0584753155708313</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1599380522966385</v>
+        <v>0.3116427659988403</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.01025268621742725</v>
+        <v>0.1653941571712494</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.03535400331020355</v>
+        <v>0.3427697420120239</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.01172066107392311</v>
+        <v>0.4314858913421631</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.006864418275654316</v>
+        <v>0.2086332440376282</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.001348887570202351</v>
+        <v>0.01886703819036484</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.01298420038074255</v>
+        <v>0.0002039722166955471</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.03428927809000015</v>
+        <v>0.1031775027513504</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.01564304158091545</v>
+        <v>0.009166251868009567</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.03766831010580063</v>
+        <v>0.01530689746141434</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.04109194874763489</v>
+        <v>0.008330035954713821</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.02570636384189129</v>
+        <v>0.0490354597568512</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.05526792630553246</v>
+        <v>0.2097459733486176</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.01633934676647186</v>
+        <v>0.06161944568157196</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.03363409638404846</v>
+        <v>0.08275046944618225</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.02832736633718014</v>
+        <v>0.09910491853952408</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.004188271705061197</v>
+        <v>0.1445600539445877</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.01674575917422771</v>
+        <v>0.02018768340349197</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.02221508882939816</v>
+        <v>0.07611195743083954</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.01936251856386662</v>
+        <v>0.000508604571223259</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.01708733290433884</v>
+        <v>0.05948436260223389</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.003895611502230167</v>
+        <v>0.04951382055878639</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0124744176864624</v>
+        <v>0.09352323412895203</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.00104653590824455</v>
+        <v>0.1808124184608459</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.004656246863305569</v>
+        <v>0.008333530277013779</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.008609585464000702</v>
+        <v>0.03843599557876587</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.02421092800796032</v>
+        <v>0.03094070218503475</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.08776984363794327</v>
+        <v>0.1872319132089615</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.01335868984460831</v>
+        <v>0.08862380683422089</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.03507036715745926</v>
+        <v>0.4422397613525391</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.002496045781299472</v>
+        <v>0.1304807364940643</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.02258223295211792</v>
+        <v>0.1642801761627197</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.007929927669465542</v>
+        <v>0.05854909494519234</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.01171571761369705</v>
+        <v>0.02219441160559654</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.04029638692736626</v>
+        <v>0.03668365627527237</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.01313638687133789</v>
+        <v>0.06635056436061859</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.03991119191050529</v>
+        <v>0.08252951502799988</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.02162308804690838</v>
+        <v>0.005435533821582794</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0217447467148304</v>
+        <v>0.2298159897327423</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01245963480323553</v>
+        <v>0.007721422240138054</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01271585654467344</v>
+        <v>0.01177136413753033</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.009902823716402054</v>
+        <v>0.04205325990915298</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.002771344967186451</v>
+        <v>0.08449987322092056</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.02065396867692471</v>
+        <v>0.02170030027627945</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.02106885612010956</v>
+        <v>0.1236213818192482</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.004700453486293554</v>
+        <v>0.03859098255634308</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.009280047379434109</v>
+        <v>0.2179605066776276</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.03627331554889679</v>
+        <v>0.4088689684867859</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.01277768239378929</v>
+        <v>0.06039644405245781</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.02348198182880878</v>
+        <v>0.01132848020642996</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.03728055208921432</v>
+        <v>0.1251221299171448</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.04255461320281029</v>
+        <v>0.07028713822364807</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.006204980425536633</v>
+        <v>0.1208190992474556</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.01234733313322067</v>
+        <v>0.06654232740402222</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.03570569306612015</v>
+        <v>0.07414604723453522</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.02350280620157719</v>
+        <v>0.02711675316095352</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.03131735697388649</v>
+        <v>0.2596611976623535</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01154238451272249</v>
+        <v>0.02425637096166611</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.01541043817996979</v>
+        <v>0.001341077731922269</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.01050635613501072</v>
+        <v>0.05504929274320602</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.01028338260948658</v>
+        <v>0.08084625750780106</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.01245170179754496</v>
+        <v>0.04032057896256447</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.003723436500877142</v>
+        <v>0.1221751123666763</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.04301793873310089</v>
+        <v>0.02574377506971359</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.002555313985794783</v>
+        <v>0.01177773997187614</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0809345468878746</v>
+        <v>0.2193761467933655</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.02334262430667877</v>
+        <v>0.03408628702163696</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.02398778684437275</v>
+        <v>0.2329308390617371</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.02870997413992882</v>
+        <v>0.01979396305978298</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.00633827643468976</v>
+        <v>0.3778641819953918</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.004401564132422209</v>
+        <v>0.1209932267665863</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.01984469220042229</v>
+        <v>0.005887344479560852</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0141372112557292</v>
+        <v>0.07676741480827332</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.008674293756484985</v>
+        <v>0.06263307482004166</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.02194651775062084</v>
+        <v>0.006970986723899841</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02489888668060303</v>
+        <v>0.02852531336247921</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.02407349459826946</v>
+        <v>0.04697307944297791</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.00433233380317688</v>
+        <v>0.01317965425550938</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0103095592930913</v>
+        <v>0.1093286871910095</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.03293828666210175</v>
+        <v>0.2247189879417419</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.005605309270322323</v>
+        <v>0.002602472901344299</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.000949217879679054</v>
+        <v>0.007208293303847313</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.03242086246609688</v>
+        <v>0.1790940165519714</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.008534189313650131</v>
+        <v>0.1811726987361908</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.02255010046064854</v>
+        <v>0.006137453019618988</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.001468360191211104</v>
+        <v>0.06863923370838165</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0115808667615056</v>
+        <v>0.04590488970279694</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.003261285601183772</v>
+        <v>0.1970280557870865</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.00641509098932147</v>
+        <v>0.1564761251211166</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0002638194710016251</v>
+        <v>0.1646332293748856</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.02340792305767536</v>
+        <v>0.01264039427042007</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.01678678393363953</v>
+        <v>0.07504937797784805</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.009965418837964535</v>
+        <v>0.2109032571315765</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.008340065367519855</v>
+        <v>0.004102444276213646</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01327290665358305</v>
+        <v>0.03811492398381233</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.005823700688779354</v>
+        <v>0.009642502292990685</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.00034783806768246</v>
+        <v>0.02949733287096024</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.009748656302690506</v>
+        <v>0.02460475452244282</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0005810922011733055</v>
+        <v>0.02208767458796501</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.03005325235426426</v>
+        <v>0.09835925698280334</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.01840411312878132</v>
+        <v>0.01265335641801357</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.02748519368469715</v>
+        <v>0.2253827750682831</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0227980762720108</v>
+        <v>0.03641394525766373</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.06262335181236267</v>
+        <v>0.09401816129684448</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.02988121658563614</v>
+        <v>0.1028342917561531</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.02264622040092945</v>
+        <v>0.08116458356380463</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.002891622018069029</v>
+        <v>0.2186702340841293</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.009258782491087914</v>
+        <v>0.06712941825389862</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.03575373440980911</v>
+        <v>0.08913308382034302</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.01755448430776596</v>
+        <v>0.000181716401129961</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.02958081662654877</v>
+        <v>0.2774396538734436</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01330294087529182</v>
+        <v>0.007520484738051891</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.01461533177644014</v>
+        <v>0.01002359949052334</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.01760885864496231</v>
+        <v>0.07268336415290833</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.006448095198720694</v>
+        <v>0.1018694341182709</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.01918680965900421</v>
+        <v>0.01559078227728605</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.00486938888207078</v>
+        <v>0.007002275437116623</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.02032821252942085</v>
+        <v>0.03665746748447418</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.01311468612402678</v>
+        <v>0.03869391232728958</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.01449966430664062</v>
+        <v>0.08911339193582535</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.003494861535727978</v>
+        <v>0.07588720321655273</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.003891127184033394</v>
+        <v>0.0004825126379728317</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.004757286049425602</v>
+        <v>0.005880843847990036</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.004529292695224285</v>
+        <v>0.1030753403902054</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.003104717936366796</v>
+        <v>0.06639703363180161</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.003411715384572744</v>
+        <v>0.1330605149269104</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0120859993621707</v>
+        <v>0.2227501720190048</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.04787691682577133</v>
+        <v>0.1457939147949219</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0160919576883316</v>
+        <v>0.3010505437850952</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.02006760239601135</v>
+        <v>0.2406103312969208</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.00553561607375741</v>
+        <v>0.0964767187833786</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.01018221117556095</v>
+        <v>0.07471565902233124</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0193505585193634</v>
+        <v>0.3397136330604553</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.01180440001189709</v>
+        <v>0.02736657857894897</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.02345414273440838</v>
+        <v>0.02544805780053139</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.00831199437379837</v>
+        <v>0.0797773078083992</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.01408960018306971</v>
+        <v>0.1317504197359085</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.005950949620455503</v>
+        <v>0.2716023921966553</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.03624389693140984</v>
+        <v>0.105400837957859</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.02112139388918877</v>
+        <v>0.1137867122888565</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.1009091734886169</v>
+        <v>0.2421340644359589</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.01361145079135895</v>
+        <v>0.04635416343808174</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.01659091934561729</v>
+        <v>0.04626495763659477</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.2688987851142883</v>
+        <v>0.07376857101917267</v>
       </c>
       <c r="B6" t="n">
-        <v>2.167846918106079</v>
+        <v>0.2241855263710022</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2260345965623856</v>
+        <v>0.04984631389379501</v>
       </c>
       <c r="D6" t="n">
-        <v>1.030507802963257</v>
+        <v>0.1154672652482986</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1742011904716492</v>
+        <v>0.0444115437567234</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4339418113231659</v>
+        <v>0.09721890836954117</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09392847865819931</v>
+        <v>0.150652140378952</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2381124198436737</v>
+        <v>0.100418284535408</v>
       </c>
       <c r="I6" t="n">
-        <v>0.343384861946106</v>
+        <v>0.07934272289276123</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5486574769020081</v>
+        <v>0.2319174706935883</v>
       </c>
       <c r="K6" t="n">
-        <v>1.676590085029602</v>
+        <v>0.2618192434310913</v>
       </c>
       <c r="L6" t="n">
-        <v>0.110769972205162</v>
+        <v>0.01890802010893822</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9713327288627625</v>
+        <v>0.3334636390209198</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1899324953556061</v>
+        <v>0.1265001744031906</v>
       </c>
       <c r="O6" t="n">
-        <v>0.58262699842453</v>
+        <v>0.1450945287942886</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1122237518429756</v>
+        <v>0.2496668547391891</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1373365521430969</v>
+        <v>0.02731508016586304</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2331275194883347</v>
+        <v>0.05320020020008087</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1204105839133263</v>
+        <v>0.07652464509010315</v>
       </c>
       <c r="T6" t="n">
-        <v>0.111943319439888</v>
+        <v>0.1259060949087143</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3569411635398865</v>
+        <v>0.1028634086251259</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2104304134845734</v>
+        <v>0.0866510272026062</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3012163043022156</v>
+        <v>0.03426513448357582</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1530975252389908</v>
+        <v>0.03548041731119156</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1356794834136963</v>
+        <v>0.04200814291834831</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3542360365390778</v>
+        <v>0.01774086616933346</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.25519198179245</v>
+        <v>0.01083974353969097</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.08099772036075592</v>
+        <v>0.1474460959434509</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2177255004644394</v>
+        <v>0.09053350985050201</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.1887730360031128</v>
+        <v>0.005605778656899929</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.2470810115337372</v>
+        <v>0.09083376079797745</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1587724238634109</v>
+        <v>0.08503037691116333</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.13949815928936</v>
+        <v>0.02834882587194443</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.06526071578264236</v>
+        <v>0.09090709686279297</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.04644219577312469</v>
+        <v>0.04307316988706589</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1463654935359955</v>
+        <v>0.03988093137741089</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.2018114179372787</v>
+        <v>0.02391824871301651</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.3792709112167358</v>
+        <v>0.1560085117816925</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.1266265958547592</v>
+        <v>0.001418676227331161</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.07088224589824677</v>
+        <v>0.01367570459842682</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.01355075836181641</v>
+        <v>0.258317619562149</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.1883607804775238</v>
+        <v>0.04522522911429405</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.00248050969094038</v>
+        <v>0.01741931587457657</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1370889842510223</v>
+        <v>0.007956557907164097</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.1106326133012772</v>
+        <v>0.03986369445919991</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.04280856624245644</v>
+        <v>0.03333231806755066</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.337491035461426</v>
+        <v>0.3732042610645294</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.06574448198080063</v>
+        <v>0.01572268269956112</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.3791719675064087</v>
+        <v>0.1062045469880104</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1843380481004715</v>
+        <v>0.210633248090744</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.3389548361301422</v>
+        <v>0.005747456103563309</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.09840445220470428</v>
+        <v>0.1304465532302856</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.03695701062679291</v>
+        <v>0.06951947510242462</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.3911211788654327</v>
+        <v>0.1010062023997307</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.03685705363750458</v>
+        <v>0.01948310062289238</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.5104407072067261</v>
+        <v>0.2611989080905914</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.3652591109275818</v>
+        <v>0.08523178100585938</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.2381309866905212</v>
+        <v>0.01272133085876703</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.2640068531036377</v>
+        <v>0.3773012459278107</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0151350311934948</v>
+        <v>0.09749739617109299</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.123801164329052</v>
+        <v>0.04147227853536606</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.1638056635856628</v>
+        <v>0.06296205520629883</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.009496245533227921</v>
+        <v>0.01554783061146736</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.1079709157347679</v>
+        <v>0.01324563939124346</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.1419033855199814</v>
+        <v>0.1786399334669113</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.1435573995113373</v>
+        <v>0.04160953685641289</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.02576944604516029</v>
+        <v>0.08069787919521332</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1070108786225319</v>
+        <v>0.1754520982503891</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.04279246926307678</v>
+        <v>0.03057317994534969</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.02139423787593842</v>
+        <v>0.001957288011908531</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.02273601666092873</v>
+        <v>0.02373919636011124</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.05755579471588135</v>
+        <v>0.04526513442397118</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.06002520769834518</v>
+        <v>0.07697772234678268</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.7109706997871399</v>
+        <v>0.1999685019254684</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.2550615072250366</v>
+        <v>0.01350705698132515</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.3246294856071472</v>
+        <v>0.1692951768636703</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.122907280921936</v>
+        <v>0.06407351046800613</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.1372204720973969</v>
+        <v>4.37609851360321e-05</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.08848150074481964</v>
+        <v>0.06694893538951874</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.1652342528104782</v>
+        <v>0.05414295196533203</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.3153463900089264</v>
+        <v>0.01122270524501801</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.1016726419329643</v>
+        <v>0.06140656769275665</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.3012810945510864</v>
+        <v>0.1338550299406052</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.1808229088783264</v>
+        <v>0.03439794853329659</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.1043796539306641</v>
+        <v>0.06668946146965027</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.06749497354030609</v>
+        <v>0.01074180658906698</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.05973276123404503</v>
+        <v>9.826384484767914e-05</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.06060513854026794</v>
+        <v>0.02974999137222767</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.05206244811415672</v>
+        <v>0.04944423213601112</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.1227643489837646</v>
+        <v>0.006583850830793381</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.2896263897418976</v>
+        <v>0.1815449446439743</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.01033738255500793</v>
+        <v>0.06194116547703743</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.078165203332901</v>
+        <v>0.1728191524744034</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.1006275042891502</v>
+        <v>0.3806942701339722</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0291626900434494</v>
+        <v>0.6589512825012207</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.02625030651688576</v>
+        <v>0.04802080988883972</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.3085836470127106</v>
+        <v>0.01900054141879082</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.1800955384969711</v>
+        <v>0.07180455327033997</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.03881963714957237</v>
+        <v>0.1239127218723297</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.071221724152565</v>
+        <v>0.09917262196540833</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.259023517370224</v>
+        <v>0.1366667002439499</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.1915374249219894</v>
+        <v>0.05035116523504257</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.1772713661193848</v>
+        <v>0.07340702414512634</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.06908813863992691</v>
+        <v>0.01843005418777466</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0713360458612442</v>
+        <v>0.01312810741364956</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.04889147728681564</v>
+        <v>0.03360342979431152</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.08961142599582672</v>
+        <v>0.01124098338186741</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.03692975640296936</v>
+        <v>0.02143514715135098</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1930591315031052</v>
+        <v>0.01281524449586868</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.05510878935456276</v>
+        <v>0.08524844795465469</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.1239358335733414</v>
+        <v>0.06893914192914963</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.6873116493225098</v>
+        <v>0.05672696977853775</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1690245270729065</v>
+        <v>0.2288165390491486</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.1029172465205193</v>
+        <v>0.1434310674667358</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.1497641205787659</v>
+        <v>0.1340788155794144</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.1055308505892754</v>
+        <v>0.1404865831136703</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.02847498655319214</v>
+        <v>0.2504231333732605</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.1617580652236938</v>
+        <v>0.2020356059074402</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.1670695692300797</v>
+        <v>0.01418935135006905</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.08027217537164688</v>
+        <v>0.08343794196844101</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.026071697473526</v>
+        <v>0.1248771250247955</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.1965509206056595</v>
+        <v>0.02814353257417679</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.260409951210022</v>
+        <v>0.02678567543625832</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.03396323695778847</v>
+        <v>0.09579582512378693</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.2631997764110565</v>
+        <v>0.02580781653523445</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.2437551766633987</v>
+        <v>0.02918720431625843</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.03467083722352982</v>
+        <v>0.01137926056981087</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.006547905504703522</v>
+        <v>0.07785762846469879</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.2148346900939941</v>
+        <v>0.1675805896520615</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0168899092823267</v>
+        <v>0.00317249377258122</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.2298632264137268</v>
+        <v>0.01733627170324326</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.04835866391658783</v>
+        <v>0.0462854877114296</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.02208052203059196</v>
+        <v>0.06660990417003632</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.003427939489483833</v>
+        <v>0.02173575013875961</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.05581986904144287</v>
+        <v>0.1376539617776871</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.06187218800187111</v>
+        <v>0.07947955280542374</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.1966679394245148</v>
+        <v>0.04016836732625961</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.1249307245016098</v>
+        <v>0.01804544776678085</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.04338138550519943</v>
+        <v>0.06728240102529526</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.01587788760662079</v>
+        <v>0.089896559715271</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.06977793574333191</v>
+        <v>0.02873285114765167</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.004781472962349653</v>
+        <v>0.0259279627352953</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.03021393902599812</v>
+        <v>0.04444294422864914</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.03667204082012177</v>
+        <v>0.02031584829092026</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.01622176915407181</v>
+        <v>0.1594242602586746</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.05700191855430603</v>
+        <v>0.107728123664856</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.1890308707952499</v>
+        <v>0.04191610962152481</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.1609675735235214</v>
+        <v>0.0290303360670805</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.01753045618534088</v>
+        <v>0.0312981940805912</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.3550366163253784</v>
+        <v>0.05942118912935257</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.2015436440706253</v>
+        <v>0.003629740327596664</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.5899460911750793</v>
+        <v>0.01376079395413399</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.1130697280168533</v>
+        <v>0.05139602720737457</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.06125722452998161</v>
+        <v>0.06208688765764236</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.2459555864334106</v>
+        <v>0.1191017180681229</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.1417983919382095</v>
+        <v>0.04719432815909386</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.1482562571763992</v>
+        <v>0.1192358210682869</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.03042279370129108</v>
+        <v>0.0410100519657135</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.05875229462981224</v>
+        <v>0.0103648453950882</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.1447367966175079</v>
+        <v>0.02364363893866539</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.06830491870641708</v>
+        <v>0.03287873044610023</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.1001589298248291</v>
+        <v>0.01010926440358162</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.05390346422791481</v>
+        <v>0.0533214658498764</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.2400548160076141</v>
+        <v>0.1638003140687943</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.1095494776964188</v>
+        <v>0.05613265186548233</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.1997198909521103</v>
+        <v>0.1540844142436981</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.1281851232051849</v>
+        <v>0.006289174780249596</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.1667510271072388</v>
+        <v>0.07250335812568665</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.004434586502611637</v>
+        <v>0.1008695065975189</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.1066276356577873</v>
+        <v>0.03952638804912567</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.1548209339380264</v>
+        <v>0.01122936606407166</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.1102595999836922</v>
+        <v>0.1275720745325089</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.3035996556282043</v>
+        <v>0.5460807085037231</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.2302833497524261</v>
+        <v>0.236061617732048</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.1683555096387863</v>
+        <v>0.2388983815908432</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.1418333500623703</v>
+        <v>0.0295530129224062</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.1316778063774109</v>
+        <v>0.08104561269283295</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.3603950142860413</v>
+        <v>0.2005569338798523</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0626063197851181</v>
+        <v>0.133012592792511</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.02467040717601776</v>
+        <v>0.0971461609005928</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.1765951067209244</v>
+        <v>0.01701595075428486</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.05632553622126579</v>
+        <v>0.1048198565840721</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.07284548878669739</v>
+        <v>0.1109239608049393</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.02943881973624229</v>
+        <v>0.1032742038369179</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.349299818277359</v>
+        <v>0.0007457993924617767</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.1924372911453247</v>
+        <v>0.2180288434028625</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.7751646041870117</v>
+        <v>0.03139288350939751</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.1024697497487068</v>
+        <v>0.01467277482151985</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0550941601395607</v>
+        <v>0.02247611060738564</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0005457373335957527</v>
+        <v>0.1184277534484863</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01053868234157562</v>
+        <v>0.3948086500167847</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001006078440696001</v>
+        <v>0.01972061395645142</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006470394786447287</v>
+        <v>0.1185600459575653</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001845031627453864</v>
+        <v>0.07416176795959473</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0005959831178188324</v>
+        <v>0.02131757512688637</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007141060777939856</v>
+        <v>0.1099023073911667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0003557808813638985</v>
+        <v>0.05207512527704239</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001537751639261842</v>
+        <v>0.108305886387825</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001470595831051469</v>
+        <v>0.06142909452319145</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009744356386363506</v>
+        <v>0.3711670637130737</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004243922594469041</v>
+        <v>0.01785298623144627</v>
       </c>
       <c r="M7" t="n">
-        <v>0.006286466494202614</v>
+        <v>0.2297580689191818</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002665905747562647</v>
+        <v>0.02609775215387344</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008838968351483345</v>
+        <v>0.04005303978919983</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0004232428036630154</v>
+        <v>0.06400813907384872</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002071931026875973</v>
+        <v>0.2696061432361603</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0006333281053230166</v>
+        <v>0.1405023634433746</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0003808639594353735</v>
+        <v>0.01096229255199432</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001108673634007573</v>
+        <v>0.1301283836364746</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002378746867179871</v>
+        <v>0.01954828388988972</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0005600826698355377</v>
+        <v>0.01175908744335175</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001522761420346797</v>
+        <v>0.0006992612034082413</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0002297920291312039</v>
+        <v>0.007275504991412163</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001267695217393339</v>
+        <v>0.008896112442016602</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0002906716545112431</v>
+        <v>0.05165655910968781</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0007428331300616264</v>
+        <v>0.03998268768191338</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001610966050066054</v>
+        <v>0.007515713572502136</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.002145219361409545</v>
+        <v>0.002271369099617004</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0004420591867528856</v>
+        <v>0.01200566254556179</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0009675590554252267</v>
+        <v>0.04286324232816696</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.001660548849031329</v>
+        <v>0.1041995137929916</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0001379124587401748</v>
+        <v>0.05346629023551941</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0005247386288829148</v>
+        <v>0.08002839982509613</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0002802582457661629</v>
+        <v>0.09189024567604065</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0001788783411029726</v>
+        <v>0.04969214648008347</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0003327950835227966</v>
+        <v>0.02571059390902519</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0005232170806266367</v>
+        <v>0.07441188395023346</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0001697190600680187</v>
+        <v>0.0477801226079464</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0003446559130679816</v>
+        <v>0.0501609779894352</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0009455060353502631</v>
+        <v>0.01984207890927792</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0005608730716630816</v>
+        <v>0.03705838695168495</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0006640608189627528</v>
+        <v>0.0783146396279335</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0001292346569243819</v>
+        <v>0.07449516654014587</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0002988274209201336</v>
+        <v>0.02391946688294411</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.001121073262766004</v>
+        <v>0.0006300536915659904</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.006050074938684702</v>
+        <v>0.2832317054271698</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.001524083316326141</v>
+        <v>0.01218216679990292</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.001867310958914459</v>
+        <v>0.01348426379263401</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0006661273073405027</v>
+        <v>0.2609342932701111</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0008537048706784844</v>
+        <v>0.05402025952935219</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8.160843572113663e-05</v>
+        <v>0.01250827126204967</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0004514218890108168</v>
+        <v>0.04332898557186127</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.075510565191507e-05</v>
+        <v>0.1251347810029984</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.00025663006817922</v>
+        <v>0.05850350111722946</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.001767597277648747</v>
+        <v>0.000524589791893959</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.001920072245411575</v>
+        <v>0.01601705886423588</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.00153843523003161</v>
+        <v>0.134025365114212</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.001190364477224648</v>
+        <v>0.03481417894363403</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0005176726263016462</v>
+        <v>0.01031625643372536</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0004006995004601777</v>
+        <v>0.0388512909412384</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.001764937420375645</v>
+        <v>0.02080424502491951</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0007687201723456383</v>
+        <v>0.04593623802065849</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0009313681512139738</v>
+        <v>0.01988057978451252</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.000292988057481125</v>
+        <v>0.03948231041431427</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.000689037493430078</v>
+        <v>0.04454676806926727</v>
       </c>
       <c r="BO7" t="n">
-        <v>9.205062815453857e-05</v>
+        <v>0.02955943532288074</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.001594634028151631</v>
+        <v>0.05219150334596634</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0002183291362598538</v>
+        <v>0.003329930827021599</v>
       </c>
       <c r="BR7" t="n">
-        <v>2.713644789764658e-05</v>
+        <v>0.06063747778534889</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0006184750236570835</v>
+        <v>0.007851636037230492</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0006972086848691106</v>
+        <v>0.005875980481505394</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0006113183917477727</v>
+        <v>0.04627698659896851</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.002872656099498272</v>
+        <v>0.2574213743209839</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0009951995452865958</v>
+        <v>0.01819270104169846</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.001331133535131812</v>
+        <v>0.03393916413187981</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0004626863228622824</v>
+        <v>0.04985574632883072</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0001804951898520812</v>
+        <v>0.03692859411239624</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0006387323956005275</v>
+        <v>0.07230103015899658</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.860463716089725e-06</v>
+        <v>0.0347956195473671</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0002894531935453415</v>
+        <v>0.02132159285247326</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0002181288000429049</v>
+        <v>0.002261936664581299</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.001876169233582914</v>
+        <v>0.09201270341873169</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0003029861545655876</v>
+        <v>0.0358927920460701</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0006109666428528726</v>
+        <v>0.05803415924310684</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0003083570918533951</v>
+        <v>0.04471179097890854</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0001239027187693864</v>
+        <v>0.01304369885474443</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0002588998759165406</v>
+        <v>0.0164137240499258</v>
       </c>
       <c r="CK7" t="n">
-        <v>7.448285032296553e-05</v>
+        <v>4.430022090673447e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0002811377926263958</v>
+        <v>0.005636067595332861</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.002406058134511113</v>
+        <v>0.144626259803772</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.00036419223761186</v>
+        <v>0.1396853923797607</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0003610383719205856</v>
+        <v>0.02794883027672768</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.001792868599295616</v>
+        <v>0.2205970287322998</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.002302913693711162</v>
+        <v>0.1145140305161476</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0006047915667295456</v>
+        <v>0.07614277303218842</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0009335863287560642</v>
+        <v>0.01660896092653275</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.001273745205253363</v>
+        <v>0.0432957261800766</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.5976358554326e-05</v>
+        <v>0.006636500358581543</v>
       </c>
       <c r="CV7" t="n">
-        <v>3.954785279347561e-05</v>
+        <v>0.01726236566901207</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.001903682947158813</v>
+        <v>0.08344316482543945</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0006342594278976321</v>
+        <v>0.0217747800052166</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0009243877721019089</v>
+        <v>0.03862050175666809</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0003619919589255005</v>
+        <v>0.04116445407271385</v>
       </c>
       <c r="DA7" t="n">
-        <v>4.866999734076671e-05</v>
+        <v>0.0211611483246088</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0003269047010689974</v>
+        <v>0.0149104343727231</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.234201019746251e-05</v>
+        <v>0.01350194960832596</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.000184796706889756</v>
+        <v>0.01674311608076096</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.001482435967773199</v>
+        <v>0.04298202320933342</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.00059193663764745</v>
+        <v>0.1278781294822693</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0004135276540182531</v>
+        <v>0.05782186239957809</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.001853878144174814</v>
+        <v>0.08911414444446564</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.001088634133338928</v>
+        <v>0.2463676631450653</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0004370123206172138</v>
+        <v>0.1141363531351089</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.0004245424643158913</v>
+        <v>0.1251210570335388</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0005721224588342011</v>
+        <v>0.04453850537538528</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.0012070641387254</v>
+        <v>0.05093647539615631</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0006814500666223466</v>
+        <v>0.01045838929712772</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.001168613322079182</v>
+        <v>0.07474708557128906</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0004192870983388275</v>
+        <v>0.03887760266661644</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0008804075187072158</v>
+        <v>0.05712506920099258</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.001332886051386595</v>
+        <v>0.01718427240848541</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0003364320145919919</v>
+        <v>0.04531452432274818</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.000172489570104517</v>
+        <v>0.004721636883914471</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.000465601944597438</v>
+        <v>0.009336862713098526</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.0002051834890153259</v>
+        <v>0.03233747556805611</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.001017051516100764</v>
+        <v>0.04617474973201752</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.00144351227208972</v>
+        <v>0.07453981041908264</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0002112413640134037</v>
+        <v>0.01388431340456009</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0004828059172723442</v>
+        <v>0.1005371734499931</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0008329624542966485</v>
+        <v>0.1074971705675125</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0008990080677904189</v>
+        <v>0.0835675448179245</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0003813159419223666</v>
+        <v>0.1152359694242477</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0001777470606612042</v>
+        <v>0.01593553274869919</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.0002586316259112209</v>
+        <v>0.08958227932453156</v>
       </c>
       <c r="EF7" t="n">
-        <v>2.747675171121955e-05</v>
+        <v>0.01403158903121948</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.001544235972687602</v>
+        <v>0.09731118381023407</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.00076176633592695</v>
+        <v>0.01547302678227425</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.001196761382743716</v>
+        <v>0.05440859496593475</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.00130279129371047</v>
+        <v>0.05408718809485435</v>
       </c>
       <c r="EK7" t="n">
-        <v>4.909229755867273e-05</v>
+        <v>0.03539605066180229</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.0003757367085199803</v>
+        <v>0.02758043818175793</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0004391949623823166</v>
+        <v>0.02562732249498367</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0001905336976051331</v>
+        <v>0.009194687008857727</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.0005271063419058919</v>
+        <v>0.004972980823367834</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.001911246683448553</v>
+        <v>0.1032747179269791</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.001016003778204322</v>
+        <v>0.03414243087172508</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0007071694708429277</v>
+        <v>0.007768689189106226</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0005470917094498873</v>
+        <v>0.01899273879826069</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0008950218325480819</v>
+        <v>0.07626898586750031</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.0007209411123767495</v>
+        <v>0.03430958837270737</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.0005980829591862857</v>
+        <v>0.007143832743167877</v>
       </c>
       <c r="EW7" t="n">
-        <v>1.387675365549512e-05</v>
+        <v>0.08403928577899933</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.000460274750366807</v>
+        <v>0.0006755702197551727</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.001940693706274033</v>
+        <v>0.1189314499497414</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0004220342671032995</v>
+        <v>0.01675242930650711</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0006509111844934523</v>
+        <v>0.06368865817785263</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0002221413451479748</v>
+        <v>0.03868937492370605</v>
       </c>
       <c r="FC7" t="n">
-        <v>3.173204459017143e-05</v>
+        <v>0.0001988573931157589</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.0002210393431596458</v>
+        <v>0.0209579411894083</v>
       </c>
       <c r="FE7" t="n">
-        <v>4.328874638304114e-06</v>
+        <v>0.006434817798435688</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.0003112719277851284</v>
+        <v>0.005268019624054432</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0002459387178532779</v>
+        <v>0.06085557863116264</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.001080388436093926</v>
+        <v>0.0702894851565361</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.001003997516818345</v>
+        <v>0.01231768168509007</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.0008047363953664899</v>
+        <v>0.08381383121013641</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0009049565414898098</v>
+        <v>0.000473417341709137</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.001392538542859256</v>
+        <v>0.06070149689912796</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.0002745497040450573</v>
+        <v>0.04348620772361755</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.0001476231263950467</v>
+        <v>0.04350440949201584</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.000411798624554649</v>
+        <v>0.005227649584412575</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.001140295993536711</v>
+        <v>0.007712509483098984</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.0006796367233619094</v>
+        <v>0.1123023852705956</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.001146791502833366</v>
+        <v>0.06445275247097015</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.0004507725825533271</v>
+        <v>0.1192042753100395</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0001626592711545527</v>
+        <v>0.07963116466999054</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.000597586331423372</v>
+        <v>0.1461951583623886</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.0001900906499940902</v>
+        <v>0.1035673096776009</v>
       </c>
       <c r="FW7" t="n">
-        <v>9.513447002973408e-05</v>
+        <v>0.008758708834648132</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0007925257086753845</v>
+        <v>0.03652249276638031</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.001296257018111646</v>
+        <v>0.04184445738792419</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0004278146952856332</v>
+        <v>0.1073446795344353</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.0001677038962952793</v>
+        <v>0.04117882624268532</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0005591920344159007</v>
+        <v>0.05852540209889412</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.0005624934565275908</v>
+        <v>0.04016684740781784</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.001318159513175488</v>
+        <v>0.03280861675739288</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.001329297199845314</v>
+        <v>0.07310282438993454</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.0001936019107233733</v>
+        <v>0.008554091677069664</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0008478211821056902</v>
+        <v>0.04860706999897957</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7.381255272775888e-05</v>
+        <v>0.01832122914493084</v>
       </c>
       <c r="B8" t="n">
-        <v>0.004544832743704319</v>
+        <v>0.0533507764339447</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003994402650278062</v>
+        <v>0.01281711738556623</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003363386727869511</v>
+        <v>0.006770888343453407</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001088334829546511</v>
+        <v>0.004031741991639137</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001303466560784727</v>
+        <v>0.002979014534503222</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0002728370018303394</v>
+        <v>0.01657284051179886</v>
       </c>
       <c r="H8" t="n">
-        <v>3.980611290899105e-05</v>
+        <v>0.01447382662445307</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009431437938474119</v>
+        <v>0.01950392872095108</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003064743068534881</v>
+        <v>0.00766049325466156</v>
       </c>
       <c r="K8" t="n">
-        <v>0.004514950327575207</v>
+        <v>0.06854897737503052</v>
       </c>
       <c r="L8" t="n">
-        <v>1.718319253996015e-05</v>
+        <v>0.01866166479885578</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00286642019636929</v>
+        <v>0.03345879912376404</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00118013983592391</v>
+        <v>0.01483936328440905</v>
       </c>
       <c r="O8" t="n">
-        <v>0.000434123445302248</v>
+        <v>0.00391953531652689</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0003985923831351101</v>
+        <v>0.0004543117829598486</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001212313072755933</v>
+        <v>0.01581556349992752</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0003042363096028566</v>
+        <v>0.02719645202159882</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0002441018150420859</v>
+        <v>0.004907018039375544</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0006317595252767205</v>
+        <v>0.01527281571179628</v>
       </c>
       <c r="U8" t="n">
-        <v>6.526752258650959e-06</v>
+        <v>0.003962784539908171</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0003163972869515419</v>
+        <v>0.006665598601102829</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0004878378822468221</v>
+        <v>0.007945912890136242</v>
       </c>
       <c r="X8" t="n">
-        <v>8.103830623440444e-06</v>
+        <v>0.003052963176742196</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0005808300920762122</v>
+        <v>0.01243514567613602</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0004658500547520816</v>
+        <v>7.054978050291538e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0004575788334477693</v>
+        <v>0.0002220301539637148</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0005754157900810242</v>
+        <v>0.009203381836414337</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0001945717958733439</v>
+        <v>0.01226490363478661</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0003382736758794636</v>
+        <v>0.002178086899220943</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0003518833545967937</v>
+        <v>0.01864746958017349</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.489826147211716e-05</v>
+        <v>0.01850849390029907</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0005360811483114958</v>
+        <v>0.007970014587044716</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0002210345264757052</v>
+        <v>0.0008056079968810081</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.924718864960596e-05</v>
+        <v>0.02784740179777145</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.556496110628359e-05</v>
+        <v>0.003662732429802418</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.000137664086651057</v>
+        <v>0.005538681522011757</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0003944344643969089</v>
+        <v>0.01107038930058479</v>
       </c>
       <c r="AM8" t="n">
-        <v>4.119988807360642e-05</v>
+        <v>0.005110002588480711</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0003709696175064892</v>
+        <v>0.001596733927726746</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0005024573183618486</v>
+        <v>0.01309893652796745</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0004512468294706196</v>
+        <v>0.006402873899787664</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0003974415012635291</v>
+        <v>0.01055223401635885</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0003914854605682194</v>
+        <v>0.01431343238800764</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0001275746326427907</v>
+        <v>0.008314212784171104</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0008034052443690598</v>
+        <v>0.009154046885669231</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.003158457344397902</v>
+        <v>0.08159969747066498</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0006108232773840427</v>
+        <v>0.00183298229239881</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.001182265928946435</v>
+        <v>0.0116156218573451</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.352514123544097e-05</v>
+        <v>0.03222277760505676</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.000572275894228369</v>
+        <v>0.009693805128335953</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0001018498878693208</v>
+        <v>0.007811366114765406</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.000379538512788713</v>
+        <v>0.002140279393643141</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.579113424872048e-05</v>
+        <v>0.001211266964673996</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.910185816697776e-05</v>
+        <v>0.003001535544171929</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.001041795942001045</v>
+        <v>0.01684811152517796</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.000933026778511703</v>
+        <v>0.003459467785432935</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0005121502908878028</v>
+        <v>9.446201147511601e-05</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0004571418394334614</v>
+        <v>8.573662489652634e-05</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0004520861839409918</v>
+        <v>0.01209424063563347</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0003208063135389239</v>
+        <v>0.01006647571921349</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.001215828815475106</v>
+        <v>0.01371149159967899</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0001050359423970804</v>
+        <v>0.02190736122429371</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0005639090086333454</v>
+        <v>0.005305448547005653</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0007042427314445376</v>
+        <v>0.02631060592830181</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0002545598545111716</v>
+        <v>0.01035882625728846</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.842747875954956e-05</v>
+        <v>0.003383088856935501</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001147009315900505</v>
+        <v>0.01674987375736237</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0002429912710795179</v>
+        <v>0.0002061361446976662</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.000262844463577494</v>
+        <v>0.02353674545884132</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0003517077420838177</v>
+        <v>0.0005766346585005522</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0003852155641652644</v>
+        <v>0.0008416913915425539</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0004433779395185411</v>
+        <v>0.0009493136312812567</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001390993595123291</v>
+        <v>0.04384488612413406</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0003968926903326064</v>
+        <v>0.00337289716117084</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0005874406197108328</v>
+        <v>0.01659857295453548</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0003946535289287567</v>
+        <v>0.005897661205381155</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.881326716102194e-05</v>
+        <v>0.0003145118243992329</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0002819298242684454</v>
+        <v>0.01516654808074236</v>
       </c>
       <c r="CB8" t="n">
-        <v>1.721601438475773e-05</v>
+        <v>0.00406805332750082</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0001172912889160216</v>
+        <v>0.007329119369387627</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.451162905956153e-06</v>
+        <v>0.001977034844458103</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0007181798573583364</v>
+        <v>0.01536818966269493</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0002128105261363089</v>
+        <v>0.006852474994957447</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0003267379361204803</v>
+        <v>0.00168666266836226</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0001585962309036404</v>
+        <v>0.004283049143850803</v>
       </c>
       <c r="CI8" t="n">
-        <v>4.205983350402676e-05</v>
+        <v>0.002192490501329303</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.000117238683742471</v>
+        <v>0.002562741981819272</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.242278449353762e-05</v>
+        <v>0.005416612140834332</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0002236509026261047</v>
+        <v>0.00166599138174206</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.00120403419714421</v>
+        <v>0.02126943320035934</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0007235056255012751</v>
+        <v>0.03864135220646858</v>
       </c>
       <c r="CO8" t="n">
-        <v>9.084046905627474e-05</v>
+        <v>0.006544455885887146</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.001190504059195518</v>
+        <v>0.02638416923582554</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.001594631350599229</v>
+        <v>0.006357487291097641</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0002711219131015241</v>
+        <v>0.009564068168401718</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0005120201967656612</v>
+        <v>0.002721950178965926</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.001143766799941659</v>
+        <v>0.004958231933414936</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0002785323595162481</v>
+        <v>0.0008879031520336866</v>
       </c>
       <c r="CV8" t="n">
-        <v>6.638366903644055e-05</v>
+        <v>0.006011534482240677</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0007114046020433307</v>
+        <v>0.01369215548038483</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0002512891660444438</v>
+        <v>0.00625205971300602</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.000556624261662364</v>
+        <v>0.005740287713706493</v>
       </c>
       <c r="CZ8" t="n">
-        <v>9.71484842011705e-05</v>
+        <v>0.001958823762834072</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.924455864354968e-05</v>
+        <v>0.0009299782104790211</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0001654684747336432</v>
+        <v>0.0001824884675443172</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.490493716322817e-05</v>
+        <v>0.002882240805774927</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0001378991437377408</v>
+        <v>0.004846992436796427</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.000438408664194867</v>
+        <v>0.005780039355158806</v>
       </c>
       <c r="DF8" t="n">
-        <v>8.536624227417633e-05</v>
+        <v>0.0003933345433324575</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.661532405705657e-05</v>
+        <v>0.0119799692183733</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0009021800942718983</v>
+        <v>0.01121377106755972</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0001821376208681613</v>
+        <v>0.03059661760926247</v>
       </c>
       <c r="DJ8" t="n">
-        <v>8.929691830417141e-05</v>
+        <v>0.02681009843945503</v>
       </c>
       <c r="DK8" t="n">
-        <v>9.508468065178022e-05</v>
+        <v>0.005893011577427387</v>
       </c>
       <c r="DL8" t="n">
-        <v>6.17506739217788e-05</v>
+        <v>0.00952417403459549</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0006411724025383592</v>
+        <v>0.001444830093532801</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0002915040531661361</v>
+        <v>0.009819241240620613</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0005622499156743288</v>
+        <v>0.01210149936378002</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0001350564562017098</v>
+        <v>0.008758655749261379</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0005325464881025255</v>
+        <v>0.02165240049362183</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0005989543860778213</v>
+        <v>0.002399394754320383</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0001895245077321306</v>
+        <v>0.002557402243837714</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0001468469999963418</v>
+        <v>0.001308432081714272</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0001745984918670729</v>
+        <v>0.0008670724928379059</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0001064985553966835</v>
+        <v>0.01381186582148075</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0001576997747179121</v>
+        <v>0.005526558496057987</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.00063669792143628</v>
+        <v>0.006140793673694134</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0002623384934850037</v>
+        <v>0.00126145756803453</v>
       </c>
       <c r="DZ8" t="n">
-        <v>8.101353887468576e-05</v>
+        <v>0.0005864668637514114</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0004646025481633842</v>
+        <v>0.01368194073438644</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0004728107305709273</v>
+        <v>0.01645257696509361</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0003261463716626167</v>
+        <v>0.005318391602486372</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.000226979173021391</v>
+        <v>0.01943947002291679</v>
       </c>
       <c r="EE8" t="n">
-        <v>7.249106420204043e-05</v>
+        <v>0.01616726815700531</v>
       </c>
       <c r="EF8" t="n">
-        <v>5.446271097753197e-05</v>
+        <v>0.001986386720091105</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0007700196001678705</v>
+        <v>0.002383573912084103</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0002860309032257646</v>
+        <v>0.004734653513878584</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0007215995574370027</v>
+        <v>0.02342248521745205</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0007716016843914986</v>
+        <v>0.008110164664685726</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0001267520128749311</v>
+        <v>0.01215715892612934</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.0001640596310608089</v>
+        <v>0.0009365232544951141</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0001491618022555485</v>
+        <v>0.002451348584145308</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0001450658601243049</v>
+        <v>0.005825258791446686</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0002221206377726048</v>
+        <v>0.003789503825828433</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.000635322357993573</v>
+        <v>3.096205182373524e-05</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0004149447486270219</v>
+        <v>0.004721084609627724</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0003608838887885213</v>
+        <v>0.007324555423110723</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0002112289657816291</v>
+        <v>0.006145134102553129</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.00016748123744037</v>
+        <v>0.01407622825354338</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0004524596151895821</v>
+        <v>8.471263572573662e-05</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0003767407033592463</v>
+        <v>0.001717033330351114</v>
       </c>
       <c r="EW8" t="n">
-        <v>3.23789099638816e-05</v>
+        <v>0.008564179763197899</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0001221062557306141</v>
+        <v>0.002864712616428733</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0007129918085411191</v>
+        <v>0.01823929324746132</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.0001918813795782626</v>
+        <v>0.004342786967754364</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0003986707306466997</v>
+        <v>0.005940263159573078</v>
       </c>
       <c r="FB8" t="n">
-        <v>5.864778722752817e-05</v>
+        <v>0.001245619961991906</v>
       </c>
       <c r="FC8" t="n">
-        <v>2.052168383670505e-05</v>
+        <v>0.004766758065670729</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0001610663603059947</v>
+        <v>0.004043577238917351</v>
       </c>
       <c r="FE8" t="n">
-        <v>4.615243233274668e-05</v>
+        <v>0.003345233853906393</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0002172275853808969</v>
+        <v>0.003445230890065432</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0002270330296596512</v>
+        <v>0.001758206519298255</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0006101974868215621</v>
+        <v>0.01304016076028347</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.0005644187913276255</v>
+        <v>0.0006684873369522393</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.0005057170055806637</v>
+        <v>0.01877764984965324</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0004585982242133468</v>
+        <v>0.0005973940715193748</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0004608035087585449</v>
+        <v>0.009572552517056465</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0002738096518442035</v>
+        <v>0.003585825441405177</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0001094992039725184</v>
+        <v>0.002057580277323723</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.000238480104599148</v>
+        <v>0.01872820034623146</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0004331252712290734</v>
+        <v>0.01423950120806694</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.0001153760676970705</v>
+        <v>0.0303992722183466</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.0007648332393728197</v>
+        <v>0.01483168639242649</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.0001077604174497537</v>
+        <v>0.006829301826655865</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0008277794695459306</v>
+        <v>0.02910345606505871</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0005351853324100375</v>
+        <v>0.0196054745465517</v>
       </c>
       <c r="FV8" t="n">
-        <v>1.296913251280785e-05</v>
+        <v>0.006225126329809427</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0003003835154231638</v>
+        <v>0.01174270547926426</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.0005370915750972927</v>
+        <v>0.0001093414612114429</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.0009429618949070573</v>
+        <v>0.0001436105230823159</v>
       </c>
       <c r="FZ8" t="n">
-        <v>6.646288238698617e-05</v>
+        <v>0.004543904680758715</v>
       </c>
       <c r="GA8" t="n">
-        <v>3.416530671529472e-05</v>
+        <v>0.01160248648375273</v>
       </c>
       <c r="GB8" t="n">
-        <v>7.122621173039079e-05</v>
+        <v>0.002273930702358484</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0005118536064401269</v>
+        <v>0.008448648266494274</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.0003229695721529424</v>
+        <v>0.001521701458841562</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.001009467290714383</v>
+        <v>0.01412265002727509</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.0002719908661674708</v>
+        <v>0.004833344370126724</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0003810050257015973</v>
+        <v>0.005737542640417814</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.05291283503174782</v>
+        <v>0.09363622218370438</v>
       </c>
       <c r="B9" t="n">
-        <v>1.284878492355347</v>
+        <v>0.4510738551616669</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4296126961708069</v>
+        <v>0.8189167976379395</v>
       </c>
       <c r="D9" t="n">
-        <v>0.11929552257061</v>
+        <v>0.3379416167736053</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3331276476383209</v>
+        <v>1.057346343994141</v>
       </c>
       <c r="F9" t="n">
-        <v>0.137767031788826</v>
+        <v>0.1753049045801163</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2184252142906189</v>
+        <v>0.2003768682479858</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02093186974525452</v>
+        <v>0.04407370090484619</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06963346153497696</v>
+        <v>0.4653582870960236</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1569467335939407</v>
+        <v>0.1387869715690613</v>
       </c>
       <c r="K9" t="n">
-        <v>1.010027170181274</v>
+        <v>0.6545229554176331</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3068231046199799</v>
+        <v>1.024140477180481</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3010075688362122</v>
+        <v>0.4663140177726746</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2897628843784332</v>
+        <v>1.13340950012207</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04979374259710312</v>
+        <v>0.4463234543800354</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2116961181163788</v>
+        <v>0.09697848558425903</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.157756581902504</v>
+        <v>0.1775705814361572</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1310828030109406</v>
+        <v>0.3039240837097168</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01711224019527435</v>
+        <v>0.02533633634448051</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1388848125934601</v>
+        <v>0.04901399090886116</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02016402781009674</v>
+        <v>0.1163391098380089</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01067466009408236</v>
+        <v>0.1647654473781586</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01801853999495506</v>
+        <v>0.07252468168735504</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0120781809091568</v>
+        <v>0.1964838206768036</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.008075266145169735</v>
+        <v>0.05932540446519852</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.2185504138469696</v>
+        <v>0.113419733941555</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.08289684355258942</v>
+        <v>0.4841834902763367</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04035739600658417</v>
+        <v>0.0808572843670845</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.231943279504776</v>
+        <v>0.0179133415222168</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.06709133833646774</v>
+        <v>0.1767799854278564</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01933136023581028</v>
+        <v>0.2403669953346252</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1682660430669785</v>
+        <v>0.0522729754447937</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.08156381547451019</v>
+        <v>0.2564233243465424</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.08997342735528946</v>
+        <v>0.2552138268947601</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.2084751278162003</v>
+        <v>0.02313799783587456</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.103243961930275</v>
+        <v>0.2176584303379059</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.2066363394260406</v>
+        <v>0.001630404032766819</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.09631550312042236</v>
+        <v>0.2511422038078308</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.09042539447546005</v>
+        <v>0.04784001410007477</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.159185066819191</v>
+        <v>0.07399569451808929</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0184575729072094</v>
+        <v>0.1369089484214783</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.2117652595043182</v>
+        <v>0.001038528978824615</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.003464937210083008</v>
+        <v>0.1115113645792007</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.05831532180309296</v>
+        <v>0.01328607276082039</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.03697944432497025</v>
+        <v>0.0775909349322319</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.08933877944946289</v>
+        <v>0.1709065139293671</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.7638591527938843</v>
+        <v>0.6713811755180359</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2003104090690613</v>
+        <v>0.05241216719150543</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.132722020149231</v>
+        <v>0.3193747103214264</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.03516751527786255</v>
+        <v>0.3765369057655334</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.2149082720279694</v>
+        <v>0.09495622664690018</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.2943102717399597</v>
+        <v>0.04800080880522728</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2625335454940796</v>
+        <v>0.1773100644350052</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.1483198255300522</v>
+        <v>0.2390216886997223</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.163678765296936</v>
+        <v>0.004025887697935104</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.3940644562244415</v>
+        <v>0.439741849899292</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.1645563244819641</v>
+        <v>0.4235053062438965</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.06172579526901245</v>
+        <v>0.09438697248697281</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.1383566409349442</v>
+        <v>0.2608214914798737</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.2173973023891449</v>
+        <v>0.2570132911205292</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.02334721945226192</v>
+        <v>0.01369159668684006</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.01094668544828892</v>
+        <v>0.2714660465717316</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.1018451452255249</v>
+        <v>0.1433485150337219</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.06420852988958359</v>
+        <v>0.08611799776554108</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.2836483716964722</v>
+        <v>0.0536944642663002</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.1038801223039627</v>
+        <v>0.06520769000053406</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.1059346124529839</v>
+        <v>0.09539066255092621</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.08817410469055176</v>
+        <v>0.3653832972049713</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0490664578974247</v>
+        <v>0.04946282505989075</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0608036145567894</v>
+        <v>0.1522946357727051</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.06523911654949188</v>
+        <v>0.04905002936720848</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.03132319822907448</v>
+        <v>0.1399512887001038</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.06780113279819489</v>
+        <v>0.09687172621488571</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.4257271885871887</v>
+        <v>0.2556846141815186</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.2978816032409668</v>
+        <v>0.08400379121303558</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.007277137134224176</v>
+        <v>0.1147746592760086</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.01090691052377224</v>
+        <v>0.2009829729795456</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.02890301123261452</v>
+        <v>0.1414172500371933</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.06913039088249207</v>
+        <v>0.1160188466310501</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.09759540110826492</v>
+        <v>0.04676596820354462</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.03085801564157009</v>
+        <v>0.4249434471130371</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.03605280816555023</v>
+        <v>0.05983458459377289</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.2070107609033585</v>
+        <v>0.2223590016365051</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002505164593458176</v>
+        <v>0.1647284030914307</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.00634063733741641</v>
+        <v>0.1801763623952866</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.08227154612541199</v>
+        <v>0.2336714267730713</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01155297458171844</v>
+        <v>0.002176383510231972</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.07814116030931473</v>
+        <v>0.05683421716094017</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.05068406090140343</v>
+        <v>0.05066736787557602</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.01267200242727995</v>
+        <v>0.130272164940834</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.2590484917163849</v>
+        <v>0.1007508933544159</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.1847249865531921</v>
+        <v>0.1765987575054169</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.08887505531311035</v>
+        <v>0.02120792493224144</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.03545897826552391</v>
+        <v>0.4506746530532837</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.06885735690593719</v>
+        <v>0.4200958907604218</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.28429114818573</v>
+        <v>0.5103970170021057</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.183955579996109</v>
+        <v>0.1330343782901764</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.05530782788991928</v>
+        <v>0.01595424860715866</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.05764798447489738</v>
+        <v>0.17635378241539</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.03199184313416481</v>
+        <v>0.06019533425569534</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.2206523269414902</v>
+        <v>0.2096637487411499</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.03466068953275681</v>
+        <v>0.2008566409349442</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0420992448925972</v>
+        <v>0.2166000157594681</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.08932497352361679</v>
+        <v>0.2107213139533997</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.03036621958017349</v>
+        <v>0.02880202420055866</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.06946554780006409</v>
+        <v>0.02802159450948238</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.06000560149550438</v>
+        <v>0.09380269050598145</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.003907665610313416</v>
+        <v>0.1968676298856735</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.2751622200012207</v>
+        <v>0.005963969975709915</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.3426823914051056</v>
+        <v>0.2225188910961151</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.02503864467144012</v>
+        <v>0.3511092662811279</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.2186309844255447</v>
+        <v>0.06718453019857407</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.04058244079351425</v>
+        <v>0.4801802039146423</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.1386847645044327</v>
+        <v>0.597669243812561</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.1503249406814575</v>
+        <v>0.1131950542330742</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.02848668023943901</v>
+        <v>0.03688093274831772</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.09646697342395782</v>
+        <v>0.1452386826276779</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.08897069096565247</v>
+        <v>0.05660152435302734</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.157251164317131</v>
+        <v>0.1257947683334351</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.07816697657108307</v>
+        <v>0.1774736195802689</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.14264777302742</v>
+        <v>0.1111114695668221</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.04564467817544937</v>
+        <v>0.3142426908016205</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.02843271195888519</v>
+        <v>0.1414165943861008</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.01068480871617794</v>
+        <v>0.2314097583293915</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.04019699618220329</v>
+        <v>0.1517811417579651</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.108589231967926</v>
+        <v>0.276052713394165</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.02551572769880295</v>
+        <v>0.01937968842685223</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.262627512216568</v>
+        <v>0.03863220661878586</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.01477217115461826</v>
+        <v>0.06054850667715073</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.004125874489545822</v>
+        <v>0.07977895438671112</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.07677779346704483</v>
+        <v>0.05199064314365387</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.07463891804218292</v>
+        <v>0.4859777092933655</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.02088662981987</v>
+        <v>0.102232038974762</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.08313113451004028</v>
+        <v>0.3209126591682434</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.05219769477844238</v>
+        <v>0.3170377016067505</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.07380074262619019</v>
+        <v>0.04514740407466888</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.1060222089290619</v>
+        <v>0.08398810029029846</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.02572616189718246</v>
+        <v>0.1188065558671951</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0214616134762764</v>
+        <v>0.1993378847837448</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.03095218166708946</v>
+        <v>0.1899292469024658</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.002873141318559647</v>
+        <v>0.01637021452188492</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0832575336098671</v>
+        <v>0.02869205176830292</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.01434414554387331</v>
+        <v>0.1338130086660385</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.007520285435020924</v>
+        <v>0.06545616686344147</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.01815728470683098</v>
+        <v>0.2035500556230545</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.05404188483953476</v>
+        <v>0.2025232166051865</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.07155322283506393</v>
+        <v>0.04956108704209328</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.149284616112709</v>
+        <v>0.3004825115203857</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.1996267288923264</v>
+        <v>0.08186529576778412</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.02478072047233582</v>
+        <v>0.1544764488935471</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.09949708729982376</v>
+        <v>0.07677933573722839</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.1620453298091888</v>
+        <v>0.06213664263486862</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.184666633605957</v>
+        <v>0.1870496273040771</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.05716963112354279</v>
+        <v>0.07237307727336884</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.2053454220294952</v>
+        <v>0.3048396706581116</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.01585168018937111</v>
+        <v>0.1689568161964417</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.001797947566956282</v>
+        <v>0.2181782424449921</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.08193829655647278</v>
+        <v>0.2116256952285767</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.05649268627166748</v>
+        <v>0.07888992130756378</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.09208114445209503</v>
+        <v>0.03171765059232712</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.02328108996152878</v>
+        <v>0.05234525725245476</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.01199749484658241</v>
+        <v>0.1717284768819809</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.001445404370315373</v>
+        <v>0.08812915533781052</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.03203977271914482</v>
+        <v>0.09692379832267761</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.01939709298312664</v>
+        <v>0.2279771417379379</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.04556862264871597</v>
+        <v>0.02901881746947765</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.03875701874494553</v>
+        <v>0.02066273987293243</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.03415737301111221</v>
+        <v>0.3655220866203308</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.01748793013393879</v>
+        <v>0.1801739484071732</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.003105692565441132</v>
+        <v>0.2540365159511566</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0310695692896843</v>
+        <v>0.2867124676704407</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.2063722461462021</v>
+        <v>0.1886142939329147</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.08533723652362823</v>
+        <v>0.243549108505249</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.1710359454154968</v>
+        <v>0.08798794448375702</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.08448255062103271</v>
+        <v>0.001857951283454895</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.1637967675924301</v>
+        <v>0.3162385523319244</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.04476757347583771</v>
+        <v>0.3590886890888214</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.04632647335529327</v>
+        <v>0.123347669839859</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.05414362624287605</v>
+        <v>0.01809155941009521</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.09173396229743958</v>
+        <v>0.1948610544204712</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0513942763209343</v>
+        <v>0.1562225222587585</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.06015174090862274</v>
+        <v>0.1579646170139313</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.1020912751555443</v>
+        <v>0.1842644959688187</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.01621756516396999</v>
+        <v>0.203762948513031</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.1621179133653641</v>
+        <v>0.009210312739014626</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.09280060231685638</v>
+        <v>0.2271948754787445</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.1395885199308395</v>
+        <v>0.2243687659502029</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.4276091456413269</v>
+        <v>0.352832555770874</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.104464516043663</v>
+        <v>0.1390492916107178</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0006612562574446201</v>
+        <v>2.884604327846318e-06</v>
       </c>
       <c r="B10" t="n">
-        <v>0.004033155273646116</v>
+        <v>1.934715510287788e-05</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001149451127275825</v>
+        <v>6.001311703585088e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0004741530865430832</v>
+        <v>1.146813701780047e-07</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002821767004206777</v>
+        <v>6.797453352191951e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0003012539527844638</v>
+        <v>3.639884198491927e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0009854130912572145</v>
+        <v>1.585634322509577e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0005739629850722849</v>
+        <v>1.852114905886992e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0005985404714010656</v>
+        <v>1.87210616786615e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0003223199455533177</v>
+        <v>2.474480425007641e-07</v>
       </c>
       <c r="K10" t="n">
-        <v>0.002772759646177292</v>
+        <v>2.166575177398045e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0005704169743694365</v>
+        <v>6.049288003850961e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0006670295842923224</v>
+        <v>2.945590495073702e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003037883434444666</v>
+        <v>8.842078386805952e-06</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0002381497615715489</v>
+        <v>7.253401577145269e-07</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001375665073283017</v>
+        <v>7.582772241221392e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0003662985982373357</v>
+        <v>1.037672745951568e-06</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0002777498448267579</v>
+        <v>2.045950168394484e-06</v>
       </c>
       <c r="S10" t="n">
-        <v>6.862768350401893e-05</v>
+        <v>2.819115820784646e-07</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0007673752261325717</v>
+        <v>3.246296955694561e-06</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0004335280100349337</v>
+        <v>7.246491691148549e-07</v>
       </c>
       <c r="V10" t="n">
-        <v>4.778802031069063e-05</v>
+        <v>2.299990910614724e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0003917884896509349</v>
+        <v>3.038702743651811e-06</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001052014296874404</v>
+        <v>1.27906275793066e-06</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.068145350785926e-05</v>
+        <v>7.327005846491375e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0003324517456348985</v>
+        <v>1.688850034042844e-06</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.213397187413648e-05</v>
+        <v>2.408591853964026e-06</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.527603646740317e-05</v>
+        <v>2.418129554371262e-07</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0009427579934708774</v>
+        <v>1.593323077031528e-06</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0002906928420998156</v>
+        <v>3.439806278038304e-06</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0006378069519996643</v>
+        <v>3.593542714952491e-06</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.879628487396985e-05</v>
+        <v>3.971639216615586e-06</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.000274783669738099</v>
+        <v>1.34862909817457e-06</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.000299845531117171</v>
+        <v>1.512015899152175e-07</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.403359682532027e-05</v>
+        <v>4.317415459809126e-06</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0005465931026265025</v>
+        <v>3.001860250151367e-06</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0001388309756293893</v>
+        <v>1.096771256925422e-06</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.001276453607715666</v>
+        <v>7.799220838933252e-06</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.019293581019156e-05</v>
+        <v>6.331747499643825e-07</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.000151246742461808</v>
+        <v>9.265039579986478e-08</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0002741387579590082</v>
+        <v>7.74227282818174e-06</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0008112804498523474</v>
+        <v>1.138784568865958e-06</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0003221405204385519</v>
+        <v>9.51068841459346e-07</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0003118754830211401</v>
+        <v>3.294267571618548e-06</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0005507200257852674</v>
+        <v>1.196530092784087e-07</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0004057747137267143</v>
+        <v>1.87241153071227e-06</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.002599030733108521</v>
+        <v>1.801163853087928e-05</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0008377791382372379</v>
+        <v>9.032060575009382e-07</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0002325821260455996</v>
+        <v>1.459772647649515e-06</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.000738188624382019</v>
+        <v>2.769860429907567e-06</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0007969052530825138</v>
+        <v>1.455284291296266e-06</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0003214649914298207</v>
+        <v>8.113649414553947e-07</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.16036481410265e-06</v>
+        <v>8.58041175888502e-07</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0004787674406543374</v>
+        <v>1.692799173724779e-06</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.170165680581704e-05</v>
+        <v>2.794502279357403e-06</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.868559360853396e-05</v>
+        <v>2.965401563415071e-06</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.620081017492339e-05</v>
+        <v>4.888574494543718e-06</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0009163011563941836</v>
+        <v>1.736239255478722e-06</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.002296439372003078</v>
+        <v>8.524199074599892e-06</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0002483344869688153</v>
+        <v>1.276868033528444e-08</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0009470775257796049</v>
+        <v>1.112195377572789e-06</v>
       </c>
       <c r="BJ10" t="n">
-        <v>4.905619061901234e-05</v>
+        <v>6.395054015229107e-07</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0002787197008728981</v>
+        <v>8.339446821992169e-07</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0007476636092178524</v>
+        <v>6.725804269080982e-07</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0002367604174651206</v>
+        <v>1.58055604515539e-06</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.038205093413126e-05</v>
+        <v>1.283528604290041e-06</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0003918470174539834</v>
+        <v>1.633799683986581e-06</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0006177083123475313</v>
+        <v>1.045732005877653e-06</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.0004794653505086899</v>
+        <v>1.366160518045945e-07</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0005920487456023693</v>
+        <v>2.613642664073268e-06</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0002078237885143608</v>
+        <v>6.662969553872244e-08</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0003427434421610087</v>
+        <v>2.034211775026051e-06</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0003925908531527966</v>
+        <v>2.240685034848866e-06</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.00170332717243582</v>
+        <v>1.290691125177545e-05</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.001175510347820818</v>
+        <v>7.594324529236474e-07</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0001351949322270229</v>
+        <v>2.999156095029321e-06</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0004936532932333648</v>
+        <v>3.419040695007425e-06</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0003482180763967335</v>
+        <v>1.36001233386196e-07</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0001800593017833307</v>
+        <v>1.511538357590325e-06</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0005267655360512435</v>
+        <v>8.723550877220987e-07</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0001623929565539584</v>
+        <v>4.41156686292743e-07</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0002056520461337641</v>
+        <v>1.232680688190158e-06</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0007689561462029815</v>
+        <v>7.150240435294108e-06</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0002317115722689778</v>
+        <v>1.835022658269736e-06</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0001938642526511103</v>
+        <v>4.761050149681978e-07</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0003730398311745375</v>
+        <v>9.710290669318056e-07</v>
       </c>
       <c r="CI10" t="n">
-        <v>9.893540118355304e-05</v>
+        <v>6.016311999701429e-07</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0001202605271828361</v>
+        <v>1.44623257369858e-07</v>
       </c>
       <c r="CK10" t="n">
-        <v>5.210406015976332e-05</v>
+        <v>5.862162879566313e-07</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0001892072177724913</v>
+        <v>1.709230303958975e-07</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.0007444237126037478</v>
+        <v>2.661583948793123e-06</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0003544061619322747</v>
+        <v>1.125359449360985e-05</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0003761612169910222</v>
+        <v>2.881862201320473e-06</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0003114840073976666</v>
+        <v>5.274290288070915e-06</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0001321208401350304</v>
+        <v>2.663988425410935e-06</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.229530698765302e-05</v>
+        <v>1.461496367483051e-06</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0004231027269270271</v>
+        <v>1.139453956966463e-06</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.000266134855337441</v>
+        <v>1.386091071253759e-06</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0003390002530068159</v>
+        <v>1.800124323381169e-06</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0002581352891866118</v>
+        <v>2.785512549507985e-07</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0007134242914617062</v>
+        <v>6.55896383250365e-06</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0001650590274948627</v>
+        <v>1.521356580269639e-06</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0001072043160093017</v>
+        <v>1.414843211478001e-07</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0001593673950992525</v>
+        <v>1.757434233695676e-07</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0002120829012710601</v>
+        <v>7.237289310069173e-07</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0001034556844388135</v>
+        <v>7.233572887344053e-07</v>
       </c>
       <c r="DC10" t="n">
-        <v>5.848862929269671e-05</v>
+        <v>1.208900926030765e-06</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0002581668086349964</v>
+        <v>7.285335072992893e-07</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.000299687497317791</v>
+        <v>1.014767576634767e-06</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.001175766112282872</v>
+        <v>3.821384325419785e-06</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0001015631496557035</v>
+        <v>2.639205376908649e-06</v>
       </c>
       <c r="DH10" t="n">
-        <v>4.926703695673496e-05</v>
+        <v>2.637060333654517e-06</v>
       </c>
       <c r="DI10" t="n">
-        <v>5.931211489951238e-05</v>
+        <v>6.605652060898137e-07</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.000276577309705317</v>
+        <v>5.156335191713879e-06</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0003338628448545933</v>
+        <v>3.788190383602341e-07</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0004994652117602527</v>
+        <v>1.498175151937176e-06</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0004668974434025586</v>
+        <v>5.617687861558807e-07</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0004587120492942631</v>
+        <v>3.9858434774942e-07</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0003029460203833878</v>
+        <v>2.998234322149074e-06</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0003595994203351438</v>
+        <v>1.565006868986529e-06</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0002446375438012183</v>
+        <v>2.281042952745338e-06</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0001936854241648689</v>
+        <v>7.699035791119968e-07</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0005711163976229727</v>
+        <v>2.150672344214399e-06</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.0002485711884219199</v>
+        <v>2.632381210787571e-07</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.0004045057285111398</v>
+        <v>3.755146281037014e-06</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0001386821386404335</v>
+        <v>3.584129672162817e-06</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0004176067304797471</v>
+        <v>2.368771220062627e-06</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0001708156341919675</v>
+        <v>5.034552941651782e-06</v>
       </c>
       <c r="DY10" t="n">
-        <v>2.71429762506159e-05</v>
+        <v>2.015742438743473e-06</v>
       </c>
       <c r="DZ10" t="n">
-        <v>9.957118891179562e-05</v>
+        <v>1.578234446242277e-06</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0003471733361948282</v>
+        <v>2.75943307315174e-06</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0007598638185299933</v>
+        <v>4.198719580017496e-06</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.520047564757988e-05</v>
+        <v>9.625016446079826e-07</v>
       </c>
       <c r="ED10" t="n">
-        <v>2.729787956923246e-05</v>
+        <v>2.60597471424262e-06</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0001477572077419609</v>
+        <v>2.733842165980604e-06</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0001261124270968139</v>
+        <v>7.333421194744005e-07</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0005690054385922849</v>
+        <v>4.365172571851872e-06</v>
       </c>
       <c r="EH10" t="n">
-        <v>5.650359526043758e-05</v>
+        <v>1.70361204254732e-07</v>
       </c>
       <c r="EI10" t="n">
-        <v>5.633209366351366e-05</v>
+        <v>1.5423177046614e-07</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0005199448205530643</v>
+        <v>5.074703608443087e-07</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0001505325781181455</v>
+        <v>6.438845616685285e-07</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0004452044377103448</v>
+        <v>5.03461592415988e-07</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0001257424155483022</v>
+        <v>4.596442408910661e-07</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0003716509381774813</v>
+        <v>1.319108832831262e-06</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0001143616973422468</v>
+        <v>5.378865353122819e-08</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0003985166258644313</v>
+        <v>5.035053618485108e-06</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0001997231156565249</v>
+        <v>2.152347775563612e-07</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0001296046539209783</v>
+        <v>6.348257670651947e-07</v>
       </c>
       <c r="ES10" t="n">
-        <v>1.689376222202554e-05</v>
+        <v>5.096010795568873e-07</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0008813848835416138</v>
+        <v>1.128779558712267e-06</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0005367221892811358</v>
+        <v>3.557464083314699e-07</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0003160448977723718</v>
+        <v>3.065853206862812e-07</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.0004320457228459418</v>
+        <v>1.21288553600607e-06</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0001270401262445375</v>
+        <v>9.181719633488683e-07</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0007510678842663765</v>
+        <v>7.684850061195903e-06</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0002863650734070688</v>
+        <v>1.706243892840575e-06</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0001735437108436599</v>
+        <v>2.292098031375644e-07</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0001903751108329743</v>
+        <v>9.299751013713831e-08</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.0001625691656954587</v>
+        <v>7.456845310116478e-07</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0001942263916134834</v>
+        <v>2.415481503703631e-08</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0001913336309371516</v>
+        <v>1.0021776688518e-06</v>
       </c>
       <c r="FF10" t="n">
-        <v>3.63751023542136e-05</v>
+        <v>6.012550102241221e-07</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0004171183391008526</v>
+        <v>2.863288557364285e-07</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0005244638887234032</v>
+        <v>1.590929969097488e-06</v>
       </c>
       <c r="FI10" t="n">
-        <v>6.33525360171916e-06</v>
+        <v>3.724620000866707e-06</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0002241393667645752</v>
+        <v>8.51935055834474e-08</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0005349604762159288</v>
+        <v>2.487300889697508e-06</v>
       </c>
       <c r="FL10" t="n">
-        <v>7.797639409545809e-05</v>
+        <v>7.384574018942658e-07</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.0004095792246516794</v>
+        <v>5.512289362741285e-07</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0003394493251107633</v>
+        <v>3.930700032128698e-08</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0004708159249275923</v>
+        <v>2.218553618149599e-06</v>
       </c>
       <c r="FP10" t="n">
-        <v>2.178677823394537e-05</v>
+        <v>4.981185156793799e-06</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0001362769980914891</v>
+        <v>7.073508641042281e-06</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.0002312864671694115</v>
+        <v>1.628880227144691e-06</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.0001218266552314162</v>
+        <v>5.178771971259266e-07</v>
       </c>
       <c r="FT10" t="n">
-        <v>4.413702117744833e-05</v>
+        <v>3.518434596117004e-06</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0005826300475746393</v>
+        <v>5.9433496062411e-06</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.0002060611150227487</v>
+        <v>1.904370037664194e-06</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0004829260578844696</v>
+        <v>1.430533075108542e-06</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0003571938432287425</v>
+        <v>6.271236088650767e-06</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0002871330361813307</v>
+        <v>7.834663620087667e-07</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0002028369344770908</v>
+        <v>4.864109996560728e-06</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0004812391707673669</v>
+        <v>1.735242221911903e-06</v>
       </c>
       <c r="GB10" t="n">
-        <v>4.513881140155718e-05</v>
+        <v>2.052925367479475e-07</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.001581502729095519</v>
+        <v>3.649674681582837e-06</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.001071073114871979</v>
+        <v>1.375003307657607e-06</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.0005216155550442636</v>
+        <v>2.073782752631814e-06</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.0006997768068686128</v>
+        <v>5.833352361150901e-07</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.000322891166433692</v>
+        <v>1.092582238015893e-06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8.329009870067239e-05</v>
+        <v>1.275087015528698e-06</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02336270362138748</v>
+        <v>1.231074929819442e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002774872817099094</v>
+        <v>1.549976104797679e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002048172056674957</v>
+        <v>7.148949862312293e-06</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001988920848816633</v>
+        <v>7.234580152726267e-06</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002035492565482855</v>
+        <v>1.098437132895924e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001053964835591614</v>
+        <v>3.231652044632938e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001037183217704296</v>
+        <v>2.007502644119086e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>0.008063461631536484</v>
+        <v>2.364978399782558e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001775227021425962</v>
+        <v>1.541772718383072e-07</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01965794712305069</v>
+        <v>1.718608109513298e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>4.530441947281361e-05</v>
+        <v>3.730965545400977e-07</v>
       </c>
       <c r="M11" t="n">
-        <v>0.004079356323927641</v>
+        <v>8.007427823031321e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0002536483807489276</v>
+        <v>1.09898901428096e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001038565067574382</v>
+        <v>1.386322219332214e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>5.853071343153715e-05</v>
+        <v>8.406370284319564e-07</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0005403266404755414</v>
+        <v>4.885982434643665e-06</v>
       </c>
       <c r="R11" t="n">
-        <v>0.005768822506070137</v>
+        <v>4.092841663805302e-06</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0002341582294320688</v>
+        <v>8.503725439368282e-07</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001946636126376688</v>
+        <v>2.065559556285734e-06</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001138636143878102</v>
+        <v>1.052849938787404e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>0.002386153908446431</v>
+        <v>1.086998508981196e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.002197902882471681</v>
+        <v>1.281879690395726e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003897880669683218</v>
+        <v>1.785498852768796e-06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0006838723784312606</v>
+        <v>9.805183935895911e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.001553182723000646</v>
+        <v>1.247909835910832e-06</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.00225256010890007</v>
+        <v>4.683370207203552e-07</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001689837547019124</v>
+        <v>1.226018639499671e-06</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.003559981007128954</v>
+        <v>3.172670517415099e-07</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0006542211631312966</v>
+        <v>1.077571482710482e-06</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.001219177152961493</v>
+        <v>3.2496641324542e-06</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0002997616829816252</v>
+        <v>9.116680530496524e-07</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0003710563760250807</v>
+        <v>1.349694116470346e-06</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0001040130009641871</v>
+        <v>2.966701799778093e-07</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.002395696006715298</v>
+        <v>5.201286057854304e-06</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.00104837235994637</v>
+        <v>1.216162559103395e-06</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.001386674586683512</v>
+        <v>6.721362524331198e-07</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.002548757009208202</v>
+        <v>7.303004849745776e-07</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0001180398612632416</v>
+        <v>2.777511554086232e-07</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.001036199042573571</v>
+        <v>1.520844307378866e-06</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.001136042177677155</v>
+        <v>1.986767983908067e-06</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.001148844952695072</v>
+        <v>1.634085037949262e-06</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0004496382316574454</v>
+        <v>6.689481892863114e-07</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.001467642257921398</v>
+        <v>3.757897957257228e-06</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.001104706665500998</v>
+        <v>2.291626287842519e-06</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.001164774992503226</v>
+        <v>2.28945714297879e-06</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.01383881084620953</v>
+        <v>1.467335187044227e-05</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0007626495789736509</v>
+        <v>1.399282950842462e-06</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.0008685665088705719</v>
+        <v>5.295924893289339e-06</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0005446179420687258</v>
+        <v>4.44815805167309e-06</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.001478083664551377</v>
+        <v>4.620086201612139e-06</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.002405058592557907</v>
+        <v>1.657797838561237e-06</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0003424095921218395</v>
+        <v>6.779093837394612e-07</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.003070775186643004</v>
+        <v>6.537239300996589e-07</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0003447241906542331</v>
+        <v>1.513011739007197e-06</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.00562224630266428</v>
+        <v>7.430930963892024e-07</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.001760504674166441</v>
+        <v>2.49718459599535e-06</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.001349360216408968</v>
+        <v>1.196619223264861e-06</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.003501481143757701</v>
+        <v>1.019854153128108e-06</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.0008694295538589358</v>
+        <v>5.661935119860573e-06</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.001468356233090162</v>
+        <v>5.544203531826497e-07</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.001284483238123357</v>
+        <v>1.272006102226442e-06</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.002266338560730219</v>
+        <v>1.055862185239675e-06</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.002641591243445873</v>
+        <v>1.166078732239839e-06</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.0008883316768333316</v>
+        <v>3.5146106256434e-06</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0005738757899962366</v>
+        <v>3.519695326303918e-07</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0006583399372175336</v>
+        <v>1.05101935332641e-06</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.002803786657750607</v>
+        <v>4.607567007042235e-06</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.002423043362796307</v>
+        <v>6.514292181236669e-07</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0008109855116344988</v>
+        <v>6.779254363209475e-06</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.001374844927340746</v>
+        <v>1.1868542060256e-07</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.00133235368411988</v>
+        <v>8.301831257995218e-07</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0008795580361038446</v>
+        <v>1.339826212642947e-06</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.007856136187911034</v>
+        <v>1.005969988909783e-05</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.001733650336973369</v>
+        <v>1.195682443722035e-06</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0005321945063769817</v>
+        <v>2.6852467271965e-06</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.002692768583074212</v>
+        <v>2.37876611208776e-06</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.002881888998672366</v>
+        <v>2.428984544167179e-06</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0005312563152983785</v>
+        <v>1.796612650650786e-06</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0006839859415777028</v>
+        <v>4.889882347924868e-07</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.002572422381490469</v>
+        <v>1.593206889083376e-06</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0001463787048123777</v>
+        <v>1.743872104498223e-07</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.004060686565935612</v>
+        <v>3.826447027677204e-06</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0001334399566985667</v>
+        <v>8.834936693347117e-08</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0001135301281465217</v>
+        <v>1.253472646567388e-06</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.001620554714463651</v>
+        <v>2.260588416902465e-06</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0004091797163709998</v>
+        <v>2.074154053843813e-06</v>
       </c>
       <c r="CJ11" t="n">
-        <v>5.629608494928107e-05</v>
+        <v>1.68786073118099e-06</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0004816144937649369</v>
+        <v>3.797539136485284e-07</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.001690298086032271</v>
+        <v>4.500316492794809e-07</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.003315122798085213</v>
+        <v>1.806136651794077e-06</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.004209502134472132</v>
+        <v>9.874380339169875e-06</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0001633681677049026</v>
+        <v>2.772739208012354e-06</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.00165894185192883</v>
+        <v>3.882359578710748e-06</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.005101311951875687</v>
+        <v>3.36399443767732e-06</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.002157430863007903</v>
+        <v>1.549570583847526e-06</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.001224013394676149</v>
+        <v>1.694400111773575e-06</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.001506214262917638</v>
+        <v>1.41326097491401e-07</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0004531486192718148</v>
+        <v>8.94777940629865e-09</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0001604544522706419</v>
+        <v>1.005613967208774e-06</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.004274424631148577</v>
+        <v>4.018704203190282e-06</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0004319754953030497</v>
+        <v>6.32225862773339e-07</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0002233618142781779</v>
+        <v>2.459367806295631e-06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.001372517668642104</v>
+        <v>1.286348606299725e-06</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.001036707544699311</v>
+        <v>2.227008053523605e-06</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0003144738147966564</v>
+        <v>9.300836154579883e-07</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0003908434882760048</v>
+        <v>3.699056208006368e-07</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.001787138637155294</v>
+        <v>3.19092066547455e-07</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.0002728519029915333</v>
+        <v>4.323247594584245e-06</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.001665363204665482</v>
+        <v>4.566693860397208e-06</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.002697970485314727</v>
+        <v>4.268625616532518e-06</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.004116757772862911</v>
+        <v>2.247256361442851e-06</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0001476274919696152</v>
+        <v>2.298272420375724e-06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.001190265873447061</v>
+        <v>7.654967362213938e-07</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.173903678543866e-05</v>
+        <v>2.822775400090904e-07</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.001219618134200573</v>
+        <v>1.008128151624987e-06</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.001401109155267477</v>
+        <v>2.220851229139953e-06</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.001455932622775435</v>
+        <v>4.625443636996351e-07</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0004226932069286704</v>
+        <v>2.011460765061202e-06</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.0004072684387210757</v>
+        <v>1.428608698006428e-07</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0004995690542273223</v>
+        <v>5.272423777569202e-07</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.00111753330565989</v>
+        <v>9.480024800723186e-07</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0003533546696417034</v>
+        <v>3.214112666682922e-06</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.000632929615676403</v>
+        <v>9.408678351974231e-07</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.001895305467769504</v>
+        <v>1.964937155207735e-06</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.001255066832527518</v>
+        <v>1.324937102253898e-06</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0003737625665962696</v>
+        <v>1.94678750631283e-06</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0006548224482685328</v>
+        <v>3.189636117895134e-06</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0001519622746855021</v>
+        <v>7.21429046279809e-07</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.001109111937694252</v>
+        <v>1.15671832645603e-06</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.001048958860337734</v>
+        <v>2.252450940432027e-06</v>
       </c>
       <c r="EB11" t="n">
-        <v>9.671784937381744e-05</v>
+        <v>1.30725663893827e-06</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0002084905281662941</v>
+        <v>3.041819581994787e-06</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.001455821911804378</v>
+        <v>7.566494559796411e-07</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.001082089496776462</v>
+        <v>1.606109435670078e-06</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0003871743974741548</v>
+        <v>1.763131422194419e-06</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.004978164564818144</v>
+        <v>1.165865455732273e-06</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0001333007530774921</v>
+        <v>5.783789447377785e-07</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0004785509954672307</v>
+        <v>1.540849666525901e-06</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0006075383280403912</v>
+        <v>1.148924866356538e-06</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0001710296201054007</v>
+        <v>3.998326519649709e-06</v>
       </c>
       <c r="EL11" t="n">
-        <v>6.287489668466151e-05</v>
+        <v>2.013297262237757e-08</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.0003946867363993078</v>
+        <v>1.728354277474864e-07</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.001436318969354033</v>
+        <v>1.230426960319164e-06</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.001762439496815205</v>
+        <v>3.891362894137274e-07</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.003628733567893505</v>
+        <v>1.63159870680829e-06</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.000691337394528091</v>
+        <v>3.925991222786251e-06</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0002149120118701831</v>
+        <v>1.218471311403846e-06</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.001230974332429469</v>
+        <v>1.747557348608098e-06</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.002393894363194704</v>
+        <v>3.126323463220615e-06</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.0007566477288492024</v>
+        <v>1.706330522210919e-06</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.001502419821918011</v>
+        <v>1.38623772727442e-06</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0008913485798984766</v>
+        <v>1.826549578254344e-06</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0002647645014803857</v>
+        <v>2.343117841974163e-07</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.004778877831995487</v>
+        <v>4.256136435287772e-06</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0003038127615582198</v>
+        <v>1.583024129558908e-07</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0001366885844618082</v>
+        <v>2.076572627629503e-06</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.001597159658558667</v>
+        <v>1.015729253595055e-06</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.001327464124187827</v>
+        <v>1.895307832455728e-06</v>
       </c>
       <c r="FD11" t="n">
-        <v>5.769139534095302e-05</v>
+        <v>1.405539023835445e-06</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.0004696795658674091</v>
+        <v>1.932408508764638e-07</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.001359249581582844</v>
+        <v>7.509101465075219e-07</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0006835695821791887</v>
+        <v>1.189064846585097e-07</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.003084840252995491</v>
+        <v>3.552278258212027e-06</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0002578579587861896</v>
+        <v>1.461656211176887e-06</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.0004422939673531801</v>
+        <v>3.56088753505901e-06</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.003384253475815058</v>
+        <v>3.956994987674989e-06</v>
       </c>
       <c r="FL11" t="n">
-        <v>5.114811938256025e-05</v>
+        <v>3.298490014458366e-07</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.0003605027159210294</v>
+        <v>3.540094439813402e-08</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0004773749387823045</v>
+        <v>2.627486082928954e-06</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0008603151654824615</v>
+        <v>1.222092578245793e-06</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.001007914310321212</v>
+        <v>4.376701326691546e-06</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.00144739099778235</v>
+        <v>2.964707164210267e-06</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.003538873977959156</v>
+        <v>1.478169451729627e-06</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.0006553047569468617</v>
+        <v>5.543444331124192e-06</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.002799359848722816</v>
+        <v>7.873684808146209e-06</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.00086970318807289</v>
+        <v>2.011366177612217e-06</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.001690570032224059</v>
+        <v>2.880651663872413e-06</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.001790181617252529</v>
+        <v>2.627708113323024e-07</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0005494948709383607</v>
+        <v>1.990934379136888e-06</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.002427867613732815</v>
+        <v>1.160314923254191e-06</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.002610424067825079</v>
+        <v>1.359324414806906e-06</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0005140374996699393</v>
+        <v>1.070274379344482e-06</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.0009871646761894226</v>
+        <v>1.234175783793034e-06</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.007613522000610828</v>
+        <v>7.751130510769144e-07</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.001762055093422532</v>
+        <v>4.462443030206487e-06</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.004010988865047693</v>
+        <v>2.667432909220224e-06</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.003500080434605479</v>
+        <v>1.382639652547368e-06</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0009835795499384403</v>
+        <v>6.591154715351877e-07</v>
       </c>
     </row>
     <row r="12">
@@ -7258,2278 +7258,2278 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0004500511568039656</v>
+        <v>0.06821578741073608</v>
       </c>
       <c r="B13" t="n">
-        <v>0.08518776297569275</v>
+        <v>0.2003569006919861</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01102020591497421</v>
+        <v>0.05473680049180984</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04086177423596382</v>
+        <v>0.1260216683149338</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02662821114063263</v>
+        <v>0.01521298941224813</v>
       </c>
       <c r="F13" t="n">
-        <v>0.005854340270161629</v>
+        <v>0.1155732944607735</v>
       </c>
       <c r="G13" t="n">
-        <v>0.006415716372430325</v>
+        <v>0.08595684170722961</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00643899105489254</v>
+        <v>0.06619151681661606</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0005556391552090645</v>
+        <v>0.0351632833480835</v>
       </c>
       <c r="J13" t="n">
-        <v>0.007371159270405769</v>
+        <v>0.03723273798823357</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06828842312097549</v>
+        <v>0.1666693985462189</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004208822268992662</v>
+        <v>0.07841063290834427</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03748126327991486</v>
+        <v>0.1642142236232758</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02357504144310951</v>
+        <v>0.04266435652971268</v>
       </c>
       <c r="O13" t="n">
-        <v>0.005192853510379791</v>
+        <v>0.09652572870254517</v>
       </c>
       <c r="P13" t="n">
-        <v>0.003820827463641763</v>
+        <v>0.08912937343120575</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.008477586321532726</v>
+        <v>0.009219156578183174</v>
       </c>
       <c r="R13" t="n">
-        <v>0.004199409391731024</v>
+        <v>0.02440455369651318</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001524303457699716</v>
+        <v>0.009263810701668262</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0155186653137207</v>
+        <v>0.02109001763164997</v>
       </c>
       <c r="U13" t="n">
-        <v>0.002577760722488165</v>
+        <v>0.02180483192205429</v>
       </c>
       <c r="V13" t="n">
-        <v>0.003625423181802034</v>
+        <v>0.03235189244151115</v>
       </c>
       <c r="W13" t="n">
-        <v>0.00325628649443388</v>
+        <v>0.04628001898527145</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01068031322211027</v>
+        <v>0.05952541902661324</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.008094320073723793</v>
+        <v>0.02067208476364613</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.003789637936279178</v>
+        <v>0.002689773682504892</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.007023593876510859</v>
+        <v>0.02690397389233112</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.008366022258996964</v>
+        <v>0.02493740431964397</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01200135610997677</v>
+        <v>0.009124176576733589</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.001455127843655646</v>
+        <v>0.02574043720960617</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.002970929723232985</v>
+        <v>0.08596169948577881</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001191296149045229</v>
+        <v>0.02055698446929455</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.006915217265486717</v>
+        <v>0.04739745333790779</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.003855893155559897</v>
+        <v>0.04516018927097321</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.002418950432911515</v>
+        <v>0.04485670477151871</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0005603365134447813</v>
+        <v>0.02253415808081627</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.004139660857617855</v>
+        <v>0.004408407025039196</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01219488773494959</v>
+        <v>0.06864193081855774</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0003039803705178201</v>
+        <v>0.02635733783245087</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.002287251641973853</v>
+        <v>0.0255596861243248</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.004059156868606806</v>
+        <v>0.01837219670414925</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.007464687339961529</v>
+        <v>0.03477936238050461</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.004114423412829638</v>
+        <v>0.01196280494332314</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.006698566488921642</v>
+        <v>0.003512805327773094</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.004660604521632195</v>
+        <v>0.02284095622599125</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.006760170683264732</v>
+        <v>0.02417739294469357</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.05259308964014053</v>
+        <v>0.09710977226495743</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0002426987048238516</v>
+        <v>0.03721601888537407</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.009613047353923321</v>
+        <v>0.03829750046133995</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.006788314320147038</v>
+        <v>0.1176460087299347</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.003541626268997788</v>
+        <v>0.07739538699388504</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.409804776310921e-05</v>
+        <v>0.01377413421869278</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.007459700107574463</v>
+        <v>0.01354577019810677</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.002560339169576764</v>
+        <v>0.01200268696993589</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.00249587488360703</v>
+        <v>0.05032165348529816</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.01151866745203733</v>
+        <v>0.06398890912532806</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.01223546452820301</v>
+        <v>0.03124759532511234</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.008789054118096828</v>
+        <v>0.006281299516558647</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.02834666334092617</v>
+        <v>0.08226849138736725</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.007659978233277798</v>
+        <v>0.02971914038062096</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.006883797701448202</v>
+        <v>0.003212450072169304</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.008661713451147079</v>
+        <v>0.03203424066305161</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.001968023600056767</v>
+        <v>0.04132888093590736</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0116042997688055</v>
+        <v>0.01770210266113281</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.001527224667370319</v>
+        <v>0.01446023304015398</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.001397106098011136</v>
+        <v>0.00308843539096415</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.001292628585360944</v>
+        <v>0.01395895797759295</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.001943792798556387</v>
+        <v>0.02919532917439938</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.008641054853796959</v>
+        <v>0.007497135549783707</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.001295113936066628</v>
+        <v>0.02659439668059349</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.001995184924453497</v>
+        <v>0.001511162263341248</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.003825169987976551</v>
+        <v>0.0005329938139766455</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.005554888397455215</v>
+        <v>0.01762488484382629</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.02894794568419456</v>
+        <v>0.08793496340513229</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.009716976433992386</v>
+        <v>0.02339939400553703</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.006787444930523634</v>
+        <v>0.06151416152715683</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.003442290239036083</v>
+        <v>0.04355353116989136</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.003290071384981275</v>
+        <v>0.09190990030765533</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.003893278772011399</v>
+        <v>0.03037426620721817</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0002383665414527059</v>
+        <v>0.02411223202943802</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.004777434282004833</v>
+        <v>0.04539009183645248</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.001415166421793401</v>
+        <v>0.02233051136136055</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.01436072681099176</v>
+        <v>0.04691217839717865</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.00231630727648735</v>
+        <v>0.01636984199285507</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.005018054042011499</v>
+        <v>0.04695264995098114</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.002693524584174156</v>
+        <v>0.006029305979609489</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.002224108669906855</v>
+        <v>0.01604046858847141</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.002424108795821667</v>
+        <v>0.001989798853173852</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.000273476354777813</v>
+        <v>0.02569322101771832</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.002903137356042862</v>
+        <v>0.004514014814049006</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.01411046367138624</v>
+        <v>0.01012520119547844</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.001727963797748089</v>
+        <v>0.05336330831050873</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.002361468505114317</v>
+        <v>0.0469224750995636</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.01078163180500269</v>
+        <v>0.06903284788131714</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01019485015422106</v>
+        <v>0.008214253932237625</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0118272053077817</v>
+        <v>0.02539419196546078</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.009008388966321945</v>
+        <v>0.04474803432822227</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.01049927156418562</v>
+        <v>0.001547227147966623</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.002430515363812447</v>
+        <v>0.04605183377861977</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0008698577876202762</v>
+        <v>0.01398231741040945</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.01409626007080078</v>
+        <v>0.03985390439629555</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.004187565762549639</v>
+        <v>0.01800796762108803</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.007769313175231218</v>
+        <v>0.05163461714982986</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.00292251561768353</v>
+        <v>0.001194560201838613</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.003820337587967515</v>
+        <v>0.01544658374041319</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.00274182902649045</v>
+        <v>0.008418219164013863</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.001060828333720565</v>
+        <v>0.02563783712685108</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.001341205555945635</v>
+        <v>0.0001142153923865408</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.006412481423467398</v>
+        <v>0.02295444905757904</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.01863856054842472</v>
+        <v>0.08105267584323883</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.002018991624936461</v>
+        <v>0.01644016057252884</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.01424324885010719</v>
+        <v>0.02776047214865685</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.002327475929632783</v>
+        <v>0.0126867163926363</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.000518689164891839</v>
+        <v>0.04252669587731361</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.007134799845516682</v>
+        <v>0.01443610526621342</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.002894967794418335</v>
+        <v>0.07610253989696503</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.002903980435803533</v>
+        <v>0.01573071628808975</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.002360703889280558</v>
+        <v>0.01606546901166439</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.004372166469693184</v>
+        <v>0.0463692806661129</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.003721655812114477</v>
+        <v>0.001104520866647363</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.003197397803887725</v>
+        <v>0.03446467220783234</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01052085030823946</v>
+        <v>0.0165533572435379</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.002475934568792582</v>
+        <v>0.01865851879119873</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.001665977528318763</v>
+        <v>0.03033257648348808</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.001453477190807462</v>
+        <v>0.01534564234316349</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.002661798149347305</v>
+        <v>0.02891058661043644</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0002655235002748668</v>
+        <v>0.0287848524749279</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.005524741485714912</v>
+        <v>0.01005571521818638</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.006165084894746542</v>
+        <v>0.04977280646562576</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.004391116555780172</v>
+        <v>0.002678664401173592</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.007492576725780964</v>
+        <v>0.02567056193947792</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.001179797807708383</v>
+        <v>0.0306137390434742</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.003732470097020268</v>
+        <v>0.006178727373480797</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.001102628419175744</v>
+        <v>0.0677768662571907</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0007589259184896946</v>
+        <v>0.02478119358420372</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.002210686216130853</v>
+        <v>0.005734746344387531</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.01018613670021296</v>
+        <v>0.03666424006223679</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.004589222837239504</v>
+        <v>0.003751889802515507</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.005273208022117615</v>
+        <v>0.04078057780861855</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.009227203205227852</v>
+        <v>0.01330293156206608</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.004302537068724632</v>
+        <v>0.01073740143328905</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.003542390186339617</v>
+        <v>0.000539110042154789</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.001282590674236417</v>
+        <v>0.01369110681116581</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.001486482564359903</v>
+        <v>0.01302030868828297</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.001549031585454941</v>
+        <v>0.004426096566021442</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.01134100370109081</v>
+        <v>0.02058493718504906</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.009079826064407825</v>
+        <v>0.02552654966711998</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.005984397139400244</v>
+        <v>0.03164704144001007</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.004727525636553764</v>
+        <v>0.03597906231880188</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.005682688672095537</v>
+        <v>0.008905305527150631</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.007421153597533703</v>
+        <v>0.02450252138078213</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.004451804328709841</v>
+        <v>0.01433620229363441</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0008325034868903458</v>
+        <v>0.05755382776260376</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.001062545226886868</v>
+        <v>0.02386360242962837</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.01483780331909657</v>
+        <v>0.05285000801086426</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.00119929586071521</v>
+        <v>0.0131538650020957</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.006877206731587648</v>
+        <v>0.05167251080274582</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.003212816081941128</v>
+        <v>0.009130795486271381</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.004208095371723175</v>
+        <v>0.01981440000236034</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.003867675084620714</v>
+        <v>0.01107571646571159</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.001228423556312919</v>
+        <v>0.02891919203102589</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.003144828137010336</v>
+        <v>0.01236908044666052</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0005157440900802612</v>
+        <v>0.009681588970124722</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.006728647742420435</v>
+        <v>0.0155819496139884</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0044255624525249</v>
+        <v>0.0313277468085289</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.006567903328686953</v>
+        <v>0.02672355063259602</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.005568984430283308</v>
+        <v>0.009364450350403786</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.00341101479716599</v>
+        <v>0.03561650961637497</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0006425430765375495</v>
+        <v>0.001268168678507209</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.003647701116278768</v>
+        <v>0.02468600682914257</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.004537694621831179</v>
+        <v>0.01206430047750473</v>
       </c>
       <c r="FP13" t="n">
-        <v>6.800018309149891e-05</v>
+        <v>0.04966020211577415</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.006468545645475388</v>
+        <v>0.03344257548451424</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.009577765129506588</v>
+        <v>0.06818090379238129</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.006853134371340275</v>
+        <v>0.05167718604207039</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.003051574341952801</v>
+        <v>0.05529025942087173</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0001047019031830132</v>
+        <v>0.003657724242657423</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.003105752635747194</v>
+        <v>0.0149849746376276</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.001678436528891325</v>
+        <v>0.05354955419898033</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.005168569274246693</v>
+        <v>0.02403024025261402</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.01154006738215685</v>
+        <v>0.03807639703154564</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.002026838716119528</v>
+        <v>0.03429115563631058</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.001668451121076941</v>
+        <v>0.04649756103754044</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.001975469756871462</v>
+        <v>0.05117694288492203</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.007941443473100662</v>
+        <v>0.02268776297569275</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.006120806559920311</v>
+        <v>0.05252609774470329</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.01755652576684952</v>
+        <v>0.05217771604657173</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0004326450871303678</v>
+        <v>0.02752243354916573</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.002265906194224954</v>
+        <v>0.006661595776677132</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.05535925179719925</v>
+        <v>0.05744203552603722</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3174886703491211</v>
+        <v>1.119231224060059</v>
       </c>
       <c r="C14" t="n">
-        <v>0.010988874360919</v>
+        <v>0.3471487760543823</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2181894779205322</v>
+        <v>0.4121266007423401</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0066636111587286</v>
+        <v>0.0994921550154686</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2958915233612061</v>
+        <v>0.7746766805648804</v>
       </c>
       <c r="G14" t="n">
-        <v>0.005960004404187202</v>
+        <v>0.1445266008377075</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1233728006482124</v>
+        <v>0.5643491148948669</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03407518193125725</v>
+        <v>0.1988386809825897</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1012487560510635</v>
+        <v>0.0298047736287117</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2789793312549591</v>
+        <v>1.744337677955627</v>
       </c>
       <c r="L14" t="n">
-        <v>0.007863309234380722</v>
+        <v>0.2031876742839813</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1638422608375549</v>
+        <v>0.5179768204689026</v>
       </c>
       <c r="N14" t="n">
-        <v>0.03916490450501442</v>
+        <v>0.279414176940918</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3136724829673767</v>
+        <v>0.7770883440971375</v>
       </c>
       <c r="P14" t="n">
-        <v>0.01019556447863579</v>
+        <v>0.1194672882556915</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.03195377439260483</v>
+        <v>0.03131221979856491</v>
       </c>
       <c r="R14" t="n">
-        <v>0.02827256917953491</v>
+        <v>0.3821096420288086</v>
       </c>
       <c r="S14" t="n">
-        <v>0.008998073637485504</v>
+        <v>0.1641527265310287</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0267365537583828</v>
+        <v>0.22629314661026</v>
       </c>
       <c r="U14" t="n">
-        <v>0.04248291626572609</v>
+        <v>0.09729559719562531</v>
       </c>
       <c r="V14" t="n">
-        <v>0.07905813306570053</v>
+        <v>0.2581011056900024</v>
       </c>
       <c r="W14" t="n">
-        <v>0.06906632333993912</v>
+        <v>0.1388403177261353</v>
       </c>
       <c r="X14" t="n">
-        <v>0.02296103164553642</v>
+        <v>0.1846189796924591</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.03660306334495544</v>
+        <v>0.1335235238075256</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.06711982935667038</v>
+        <v>0.5698568224906921</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.04529063403606415</v>
+        <v>0.007169030606746674</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.007990628480911255</v>
+        <v>0.2824035286903381</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.002704596612602472</v>
+        <v>0.1279817670583725</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.01059477776288986</v>
+        <v>0.2330227494239807</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.02708688005805016</v>
+        <v>0.1261755526065826</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.03579015657305717</v>
+        <v>0.8246283531188965</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.02104637958109379</v>
+        <v>0.2154811024665833</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.02478798292577267</v>
+        <v>0.1175950914621353</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.02453099004924297</v>
+        <v>0.3566141724586487</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.03552081808447838</v>
+        <v>0.0880265086889267</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.04701521992683411</v>
+        <v>0.08690159022808075</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.05648794397711754</v>
+        <v>0.07649015635251999</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0139862010255456</v>
+        <v>0.01550338231027126</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.01989784650504589</v>
+        <v>0.1529387235641479</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.02315114811062813</v>
+        <v>0.04360223934054375</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.04392436891794205</v>
+        <v>0.05325246602296829</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.003157365601509809</v>
+        <v>0.2012018114328384</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.03157214820384979</v>
+        <v>0.5278529524803162</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.04756844416260719</v>
+        <v>0.2172635793685913</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.02412237226963043</v>
+        <v>0.407402515411377</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.2103803306818008</v>
+        <v>1.448174953460693</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.001958866603672504</v>
+        <v>0.03004846908152103</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.06018774583935738</v>
+        <v>0.04797996580600739</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.01197725627571344</v>
+        <v>0.08498331159353256</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.1650361120700836</v>
+        <v>0.4131881892681122</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0112859820947051</v>
+        <v>0.004870828241109848</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.05741840228438377</v>
+        <v>0.002515535801649094</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.08001890778541565</v>
+        <v>0.2363477945327759</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.05026061460375786</v>
+        <v>0.2037521600723267</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.06172805279493332</v>
+        <v>0.05029671639204025</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.08515933156013489</v>
+        <v>0.2091689705848694</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.02347493916749954</v>
+        <v>0.3135219812393188</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.04143053293228149</v>
+        <v>0.08056993782520294</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.07756727188825607</v>
+        <v>0.07851687073707581</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.02161304466426373</v>
+        <v>0.1545180678367615</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.04438707232475281</v>
+        <v>0.134374588727951</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.03191538900136948</v>
+        <v>0.04370910301804543</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.002962388098239899</v>
+        <v>0.2756215929985046</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.07104909420013428</v>
+        <v>0.166525661945343</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.02940400689840317</v>
+        <v>0.01114581152796745</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.05091632530093193</v>
+        <v>0.122942253947258</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.008654103614389896</v>
+        <v>0.0459321103990078</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.01120568253099918</v>
+        <v>0.01025660336017609</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.03024028614163399</v>
+        <v>0.4545844197273254</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.01093421783298254</v>
+        <v>0.01068134605884552</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0009063617326319218</v>
+        <v>0.1056577414274216</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.01691419258713722</v>
+        <v>0.03108601272106171</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.1230923756957054</v>
+        <v>0.8280467987060547</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.03320068120956421</v>
+        <v>0.04056176170706749</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0632326602935791</v>
+        <v>0.3532847166061401</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.02922666445374489</v>
+        <v>0.128712996840477</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.09298897534608841</v>
+        <v>0.2539444267749786</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.02415979094803333</v>
+        <v>0.1156920567154884</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.01819428987801075</v>
+        <v>0.2167616188526154</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.05867551267147064</v>
+        <v>0.1854980289936066</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.008645019493997097</v>
+        <v>0.07326015830039978</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.04132042452692986</v>
+        <v>0.3052713572978973</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.04555577412247658</v>
+        <v>0.07809619605541229</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.03530909493565559</v>
+        <v>0.08993060886859894</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.01314609032124281</v>
+        <v>0.02136250212788582</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.05015483871102333</v>
+        <v>0.2013620138168335</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.02475790679454803</v>
+        <v>0.175894483923912</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.02655985578894615</v>
+        <v>0.00031241774559021</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.03554335236549377</v>
+        <v>0.01407250761985779</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.05979827046394348</v>
+        <v>0.1604478061199188</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.01210787892341614</v>
+        <v>0.7211753129959106</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.01339507102966309</v>
+        <v>0.0359470546245575</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.04745388776063919</v>
+        <v>0.1898859441280365</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.005616237409412861</v>
+        <v>0.2281380295753479</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0223552081733942</v>
+        <v>0.007936142385005951</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.05316482484340668</v>
+        <v>0.01127541437745094</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.04320019111037254</v>
+        <v>0.381265789270401</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.01219091471284628</v>
+        <v>0.1243668347597122</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.001248497981578112</v>
+        <v>0.0003068596124649048</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.03789465501904488</v>
+        <v>0.3425037860870361</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.03998122364282608</v>
+        <v>0.04988520219922066</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.05241549387574196</v>
+        <v>0.1451523751020432</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.01738901436328888</v>
+        <v>0.06003608554601669</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.05900216847658157</v>
+        <v>0.2571140229701996</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.02433867380023003</v>
+        <v>0.07039535790681839</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.04269960522651672</v>
+        <v>0.004459109157323837</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.02051994204521179</v>
+        <v>0.000805507181212306</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.002480174880474806</v>
+        <v>0.08879753202199936</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.003444228786975145</v>
+        <v>0.1679295897483826</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.02505621686577797</v>
+        <v>0.2252857685089111</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.1641130149364471</v>
+        <v>0.136436715722084</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.03177056089043617</v>
+        <v>0.5929008722305298</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.02995575033128262</v>
+        <v>0.1384919136762619</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.001170304603874683</v>
+        <v>0.1701021790504456</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.04987286031246185</v>
+        <v>0.04260239005088806</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.03263617306947708</v>
+        <v>0.2577601373195648</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.009509710595011711</v>
+        <v>0.205079972743988</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.001730450429022312</v>
+        <v>0.1824994087219238</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.01704589836299419</v>
+        <v>0.02485395781695843</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0178047027438879</v>
+        <v>0.1824816465377808</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.006711540278047323</v>
+        <v>0.1491026878356934</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.000803682254627347</v>
+        <v>0.0448094829916954</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.03697421029210091</v>
+        <v>0.07095339149236679</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.002408304251730442</v>
+        <v>0.459166407585144</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.06572901457548141</v>
+        <v>0.08925585448741913</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.008560359477996826</v>
+        <v>0.322424054145813</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.01128257904201746</v>
+        <v>0.1994596719741821</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.05177261680364609</v>
+        <v>0.1243943572044373</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.00178917869925499</v>
+        <v>0.004778005182743073</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.005296017043292522</v>
+        <v>0.2284572422504425</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.03926538676023483</v>
+        <v>0.4045743346214294</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.002475160174071789</v>
+        <v>0.1704580187797546</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.003738285508006811</v>
+        <v>0.07282634824514389</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.005003626924008131</v>
+        <v>0.02509631961584091</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.02210783585906029</v>
+        <v>0.09163296967744827</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.04721254855394363</v>
+        <v>0.0369088239967823</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.03466859087347984</v>
+        <v>0.03566905483603477</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.01118157804012299</v>
+        <v>0.182577058672905</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.002563445828855038</v>
+        <v>0.1525948494672775</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.06269587576389313</v>
+        <v>0.1059960052371025</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.03121474385261536</v>
+        <v>0.1374958157539368</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.004615014418959618</v>
+        <v>0.06937650591135025</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.0134909488260746</v>
+        <v>0.08736708760261536</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.003926843404769897</v>
+        <v>0.0183616578578949</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.01305204071104527</v>
+        <v>0.07806969434022903</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.04261325299739838</v>
+        <v>0.04912466928362846</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.03744550421833992</v>
+        <v>0.2899990379810333</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.006714091636240482</v>
+        <v>0.1242626458406448</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.02015326358377934</v>
+        <v>0.1219569742679596</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.03781123831868172</v>
+        <v>0.06914865970611572</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.106072410941124</v>
+        <v>0.06270931661128998</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.01859735511243343</v>
+        <v>0.03248818218708038</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.0001904792152345181</v>
+        <v>0.03825557976961136</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.03309888765215874</v>
+        <v>0.4018178582191467</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.03620557859539986</v>
+        <v>0.1121841743588448</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0453416183590889</v>
+        <v>0.1013485118746758</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.01572274975478649</v>
+        <v>0.108603447675705</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.04463938996195793</v>
+        <v>0.2252626568078995</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.03907161951065063</v>
+        <v>0.1743611097335815</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.02383705973625183</v>
+        <v>0.0709187388420105</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.03486043587327003</v>
+        <v>0.01503636874258518</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.01923350803554058</v>
+        <v>0.1386436223983765</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.02114219032227993</v>
+        <v>0.3140089511871338</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.03542307764291763</v>
+        <v>0.1635433882474899</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.05501128733158112</v>
+        <v>0.2180773317813873</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.009236305952072144</v>
+        <v>0.02403498440980911</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.03466933220624924</v>
+        <v>0.02694959565997124</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.02010621689260006</v>
+        <v>0.1938605606555939</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.02857813611626625</v>
+        <v>0.2815745770931244</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.02293237112462521</v>
+        <v>3.106892108917236e-05</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.01748957671225071</v>
+        <v>0.3711023926734924</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.03529844805598259</v>
+        <v>0.06415677070617676</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.04809166491031647</v>
+        <v>0.04408971592783928</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.03609425574541092</v>
+        <v>0.4745547771453857</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.03726711124181747</v>
+        <v>0.2053891569375992</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.02234006300568581</v>
+        <v>0.0820167064666748</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.05198965221643448</v>
+        <v>0.1952361762523651</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.004481951706111431</v>
+        <v>0.05000103265047073</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.005966938100755215</v>
+        <v>0.03394823893904686</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.07242996245622635</v>
+        <v>0.2261876463890076</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.032878577709198</v>
+        <v>0.1225862354040146</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.02870291657745838</v>
+        <v>0.02147120051085949</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.01979239843785763</v>
+        <v>0.01671361178159714</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.01923367381095886</v>
+        <v>0.1650046706199646</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0253418255597353</v>
+        <v>0.1649375408887863</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.2122280299663544</v>
+        <v>0.05688531696796417</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.009453952312469482</v>
+        <v>0.477928638458252</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.04308639466762543</v>
+        <v>0.1608759462833405</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.0004355477867648005</v>
+        <v>0.03875435516238213</v>
       </c>
       <c r="B15" t="n">
-        <v>0.003400704590603709</v>
+        <v>0.04458311945199966</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0003368426114320755</v>
+        <v>0.0009127631783485413</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0005989474011585116</v>
+        <v>0.0114422719925642</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0002333822194486856</v>
+        <v>0.02201899141073227</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0005293346475809813</v>
+        <v>0.01420530676841736</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003776526427827775</v>
+        <v>0.0225314274430275</v>
       </c>
       <c r="H15" t="n">
-        <v>1.695036189630628e-06</v>
+        <v>0.01337605249136686</v>
       </c>
       <c r="I15" t="n">
-        <v>0.000267767405603081</v>
+        <v>0.0218808688223362</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0007242378778755665</v>
+        <v>0.02948403358459473</v>
       </c>
       <c r="K15" t="n">
-        <v>0.002876968821510673</v>
+        <v>0.06689970195293427</v>
       </c>
       <c r="L15" t="n">
-        <v>9.392402716912329e-05</v>
+        <v>0.006561039481312037</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0006835520034655929</v>
+        <v>0.01658538170158863</v>
       </c>
       <c r="N15" t="n">
-        <v>0.000185329801752232</v>
+        <v>0.02580270916223526</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0007576547795906663</v>
+        <v>0.01309224590659142</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0004775997949764132</v>
+        <v>0.001900528557598591</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0005765477544628084</v>
+        <v>0.02354151755571365</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0004068640701007098</v>
+        <v>0.02132664620876312</v>
       </c>
       <c r="S15" t="n">
-        <v>8.474945207126439e-05</v>
+        <v>0.001857802039012313</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0003640648501459509</v>
+        <v>0.009698201902210712</v>
       </c>
       <c r="U15" t="n">
-        <v>6.615032907575369e-05</v>
+        <v>0.006379330065101385</v>
       </c>
       <c r="V15" t="n">
-        <v>7.503205415559933e-05</v>
+        <v>0.00865559559315443</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0001563478872412816</v>
+        <v>0.00129716785158962</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0003098959568887949</v>
+        <v>0.008328877389431</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0001099360597436316</v>
+        <v>0.002721777651458979</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0006583693902939558</v>
+        <v>0.0001297465059906244</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0002298653853358701</v>
+        <v>0.01169276610016823</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.0001827789819799364</v>
+        <v>0.007962784729897976</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0004117718490306288</v>
+        <v>0.003772813826799393</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.963819861179218e-05</v>
+        <v>0.002928078174591064</v>
       </c>
       <c r="AE15" t="n">
-        <v>7.620483302162029e-07</v>
+        <v>0.01834602281451225</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0002195014094468206</v>
+        <v>0.02183477766811848</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0003289124288130552</v>
+        <v>0.004788389429450035</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0001711391232674941</v>
+        <v>0.003871728200465441</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0002034828648902476</v>
+        <v>0.01633180305361748</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.676200665518991e-06</v>
+        <v>0.00381403136998415</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0002137455740012228</v>
+        <v>0.01534505188465118</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.000396250223275274</v>
+        <v>0.004571069031953812</v>
       </c>
       <c r="AM15" t="n">
-        <v>3.755048965103924e-07</v>
+        <v>0.00909464992582798</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.272886584047228e-05</v>
+        <v>0.0003743416164070368</v>
       </c>
       <c r="AO15" t="n">
-        <v>6.871948426123708e-05</v>
+        <v>0.009861207567155361</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.0002280305197928101</v>
+        <v>0.005318255163729191</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.158342097885907e-05</v>
+        <v>0.004630422219634056</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.89994368358748e-05</v>
+        <v>0.007245976012200117</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.0003081467875745147</v>
+        <v>0.003225937020033598</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.1028848499991e-05</v>
+        <v>0.0106450030580163</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.002060191007331014</v>
+        <v>0.06261588633060455</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.000374277908122167</v>
+        <v>0.001272629597224295</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.000273805228061974</v>
+        <v>0.002966760657727718</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.000297548744129017</v>
+        <v>0.0266241692006588</v>
       </c>
       <c r="AY15" t="n">
-        <v>6.948295776965097e-05</v>
+        <v>0.009708888828754425</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.0002240018220618367</v>
+        <v>0.005014442838728428</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.0002262297493871301</v>
+        <v>0.01091290451586246</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.015500836540014e-05</v>
+        <v>0.0212775431573391</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.773715722374618e-05</v>
+        <v>0.009556938894093037</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.0007036681636236608</v>
+        <v>0.0148300863802433</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.00056155287893489</v>
+        <v>0.001071400125510991</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.611510379007086e-05</v>
+        <v>0.001596473157405853</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.0003500531311146915</v>
+        <v>0.003587378421798348</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.0002790304424706846</v>
+        <v>0.008242272771894932</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.0003194206510670483</v>
+        <v>0.007943346165120602</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.0003734519414138049</v>
+        <v>0.02540509589016438</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.0001374300773022696</v>
+        <v>0.005761557724326849</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.0001570351159898564</v>
+        <v>0.006931195501238108</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.0001298647403018549</v>
+        <v>0.02922140434384346</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.0002811656740959734</v>
+        <v>0.002257385523989797</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.773803811985999e-05</v>
+        <v>0.008166392333805561</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.000102354068076238</v>
+        <v>0.02116015739738941</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.0003471362288109958</v>
+        <v>0.002551144454628229</v>
       </c>
       <c r="BR15" t="n">
-        <v>3.810450289165601e-05</v>
+        <v>0.02647482417523861</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.0004670866183005273</v>
+        <v>0.01247815974056721</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.0004255163657944649</v>
+        <v>0.005627583246678114</v>
       </c>
       <c r="BU15" t="n">
-        <v>8.236389112425968e-05</v>
+        <v>0.0020517916418612</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.001179649378173053</v>
+        <v>0.02813323587179184</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.000408107036491856</v>
+        <v>0.002975731156766415</v>
       </c>
       <c r="BX15" t="n">
-        <v>3.494908742140979e-05</v>
+        <v>0.003490466624498367</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.0002773083106148988</v>
+        <v>0.005458567757159472</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.0001300857402384281</v>
+        <v>0.004987392108887434</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.839693767484277e-05</v>
+        <v>0.003900005016475916</v>
       </c>
       <c r="CB15" t="n">
-        <v>7.045155507512391e-05</v>
+        <v>0.005131760612130165</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.0001861953205661848</v>
+        <v>0.0116499550640583</v>
       </c>
       <c r="CD15" t="n">
-        <v>7.672399806324393e-05</v>
+        <v>0.01038032490760088</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.0005946413730271161</v>
+        <v>0.008828642778098583</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.0001558264484629035</v>
+        <v>0.002034422941505909</v>
       </c>
       <c r="CG15" t="n">
-        <v>7.396775617962703e-05</v>
+        <v>0.00598552729934454</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.0001717492705211043</v>
+        <v>0.01087019965052605</v>
       </c>
       <c r="CI15" t="n">
-        <v>3.823714723694138e-05</v>
+        <v>0.003155945101752877</v>
       </c>
       <c r="CJ15" t="n">
-        <v>8.276706648757681e-05</v>
+        <v>0.003059294307604432</v>
       </c>
       <c r="CK15" t="n">
-        <v>6.631865107920021e-05</v>
+        <v>0.002540000714361668</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.0002159695577574894</v>
+        <v>0.004675797186791897</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.0005122237489558756</v>
+        <v>0.01976074650883675</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.000357895769411698</v>
+        <v>0.04749467968940735</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.0001111220772145316</v>
+        <v>0.006121935322880745</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.0007673278450965881</v>
+        <v>0.01279842853546143</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.0008639927837066352</v>
+        <v>0.006597997155040503</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.0003691545862238854</v>
+        <v>0.01191364508122206</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.0005448838928714395</v>
+        <v>0.01248699054121971</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0001539588993182406</v>
+        <v>0.005232776515185833</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.0004055348690599203</v>
+        <v>0.008706619031727314</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.211744504165836e-05</v>
+        <v>0.004953759256750345</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.0005960557027719915</v>
+        <v>0.008099864237010479</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.0002036307705566287</v>
+        <v>0.0001580467214807868</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.0001883646473288536</v>
+        <v>0.0117822177708149</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.0002316766476724297</v>
+        <v>0.001317952759563923</v>
       </c>
       <c r="DA15" t="n">
-        <v>9.556159056955948e-05</v>
+        <v>0.004660711623728275</v>
       </c>
       <c r="DB15" t="n">
-        <v>9.611576388124377e-05</v>
+        <v>0.0002895321231335402</v>
       </c>
       <c r="DC15" t="n">
-        <v>6.286141433520243e-05</v>
+        <v>0.0002249907702207565</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.0001566159335197881</v>
+        <v>0.006726115010678768</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.0001386668591294438</v>
+        <v>0.00414911936968565</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.0002793571329675615</v>
+        <v>0.01103971526026726</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.0001111840829253197</v>
+        <v>0.0129199605435133</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.0005378327332437038</v>
+        <v>0.004813903942704201</v>
       </c>
       <c r="DI15" t="n">
-        <v>8.402029925491661e-05</v>
+        <v>0.01723647676408291</v>
       </c>
       <c r="DJ15" t="n">
-        <v>7.842494960641488e-05</v>
+        <v>0.006526663433760405</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.000346392480423674</v>
+        <v>0.0003187850816175342</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.0001741774467518553</v>
+        <v>0.0007004775106906891</v>
       </c>
       <c r="DM15" t="n">
-        <v>7.296843978110701e-05</v>
+        <v>0.007291587069630623</v>
       </c>
       <c r="DN15" t="n">
-        <v>6.799125912948512e-06</v>
+        <v>0.001091713085770607</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.0003490174422040582</v>
+        <v>0.001780332997441292</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.000174919594428502</v>
+        <v>0.001737127779051661</v>
       </c>
       <c r="DQ15" t="n">
-        <v>4.777351568918675e-05</v>
+        <v>0.0009279726073145866</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.642764103366062e-05</v>
+        <v>0.00653443206101656</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.0002158421993954107</v>
+        <v>0.006982904393225908</v>
       </c>
       <c r="DT15" t="n">
-        <v>3.742936678463593e-05</v>
+        <v>0.0008645565249025822</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.0001433300494682044</v>
+        <v>0.004216740373522043</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.0003134184225928038</v>
+        <v>0.01006609387695789</v>
       </c>
       <c r="DW15" t="n">
-        <v>3.080637543462217e-05</v>
+        <v>0.02048251964151859</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.0002130119682988152</v>
+        <v>0.007187034003436565</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.659772770944983e-05</v>
+        <v>0.00327748991549015</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.0001214869189425372</v>
+        <v>3.319096867926419e-05</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.0001084316245396622</v>
+        <v>0.0082441670820117</v>
       </c>
       <c r="EB15" t="n">
-        <v>6.229026621440426e-05</v>
+        <v>0.003103264840319753</v>
       </c>
       <c r="EC15" t="n">
-        <v>8.423534745816141e-05</v>
+        <v>0.005371542647480965</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.0004284714523237199</v>
+        <v>0.004867749754339457</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.0001019485134747811</v>
+        <v>0.0003842455334961414</v>
       </c>
       <c r="EF15" t="n">
-        <v>9.823310392675921e-06</v>
+        <v>0.01416939869523048</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.0006350360345095396</v>
+        <v>0.002758929971605539</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.0002063645224552602</v>
+        <v>0.005135760642588139</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.0001083858733181842</v>
+        <v>0.007013536524027586</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0001053168380167335</v>
+        <v>0.005545830354094505</v>
       </c>
       <c r="EK15" t="n">
-        <v>1.001514465315267e-05</v>
+        <v>0.0005385372787714005</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.0001278854324482381</v>
+        <v>0.005138152278959751</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.0001300274161621928</v>
+        <v>0.0007314245449379086</v>
       </c>
       <c r="EN15" t="n">
-        <v>7.868478132877499e-05</v>
+        <v>0.009210733696818352</v>
       </c>
       <c r="EO15" t="n">
-        <v>8.465003338642418e-05</v>
+        <v>0.007165036164224148</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0003456895938143134</v>
+        <v>0.008434672839939594</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.0003815854724962264</v>
+        <v>0.007360029965639114</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.0003324073040857911</v>
+        <v>0.006658745929598808</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.0002961840364150703</v>
+        <v>0.00684870732948184</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.0002476608497090638</v>
+        <v>0.004917141981422901</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.0002128676569554955</v>
+        <v>0.003972354345023632</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.0004080553771927953</v>
+        <v>0.002138830721378326</v>
       </c>
       <c r="EW15" t="n">
-        <v>8.463353151455522e-05</v>
+        <v>0.003701708279550076</v>
       </c>
       <c r="EX15" t="n">
-        <v>1.906008037622087e-05</v>
+        <v>0.008406382985413074</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.0006060179439373314</v>
+        <v>0.01421589218080044</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.000130824075313285</v>
+        <v>0.0003599152259994298</v>
       </c>
       <c r="FA15" t="n">
-        <v>8.168350905179977e-05</v>
+        <v>0.008438019081950188</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.0002828897850122303</v>
+        <v>0.002743577118963003</v>
       </c>
       <c r="FC15" t="n">
-        <v>9.814483928494155e-05</v>
+        <v>0.004817582666873932</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.0001718972634989768</v>
+        <v>0.004302696790546179</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.0001002867356874049</v>
+        <v>0.002321151085197926</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.0002289781987201422</v>
+        <v>0.005308871623128653</v>
       </c>
       <c r="FG15" t="n">
-        <v>3.225773252779618e-05</v>
+        <v>0.001398822292685509</v>
       </c>
       <c r="FH15" t="n">
-        <v>4.478415212361142e-05</v>
+        <v>0.01617537811398506</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.0003043291508220136</v>
+        <v>0.005491327494382858</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.000386731990147382</v>
+        <v>0.01238161791115999</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.0001280438300454989</v>
+        <v>0.01788966543972492</v>
       </c>
       <c r="FL15" t="n">
-        <v>9.682196832727641e-05</v>
+        <v>0.002772946609184146</v>
       </c>
       <c r="FM15" t="n">
-        <v>6.397851393558085e-06</v>
+        <v>0.00196996470913291</v>
       </c>
       <c r="FN15" t="n">
-        <v>4.899633859167807e-05</v>
+        <v>0.007007529027760029</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.0001046449906425551</v>
+        <v>0.008313189260661602</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0003853179514408112</v>
+        <v>0.006870585959404707</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.0003506226057652384</v>
+        <v>0.009073603898286819</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.0003890929510816932</v>
+        <v>0.007169227115809917</v>
       </c>
       <c r="FS15" t="n">
-        <v>4.810179234482348e-05</v>
+        <v>0.008518640883266926</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.0003988270764239132</v>
+        <v>0.03416247665882111</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.0002532483777031302</v>
+        <v>0.02209050208330154</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.0001705739705357701</v>
+        <v>0.01080233417451382</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.0004068722191732377</v>
+        <v>0.01452729105949402</v>
       </c>
       <c r="FX15" t="n">
-        <v>7.662466668989509e-05</v>
+        <v>0.02397014945745468</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.0005036868387833238</v>
+        <v>0.003084084950387478</v>
       </c>
       <c r="FZ15" t="n">
-        <v>9.89544641925022e-05</v>
+        <v>0.004586196504533291</v>
       </c>
       <c r="GA15" t="n">
-        <v>4.389482637634501e-05</v>
+        <v>0.006497418507933617</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.0001125926864915527</v>
+        <v>0.001769666094332933</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.0006107566296122968</v>
+        <v>0.01129921153187752</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.0005585988401435316</v>
+        <v>0.0137202050536871</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.0009427065961062908</v>
+        <v>0.01531395316123962</v>
       </c>
       <c r="GF15" t="n">
-        <v>5.416048225015402e-05</v>
+        <v>0.01896244660019875</v>
       </c>
       <c r="GG15" t="n">
-        <v>8.572779915994033e-05</v>
+        <v>0.005353387910872698</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0003495492273941636</v>
+        <v>2.73563660613263e-08</v>
       </c>
       <c r="B16" t="n">
-        <v>0.003374780528247356</v>
+        <v>1.118864645377471e-07</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0003176979662384838</v>
+        <v>1.377160696591773e-08</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0006953549454919994</v>
+        <v>2.737264281904572e-08</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001923490199260414</v>
+        <v>2.064702009363373e-08</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0002503221621736884</v>
+        <v>5.538723257814127e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000774531508795917</v>
+        <v>1.580885111707175e-08</v>
       </c>
       <c r="H16" t="n">
-        <v>0.000142327044159174</v>
+        <v>1.347611444657559e-08</v>
       </c>
       <c r="I16" t="n">
-        <v>0.000185224023880437</v>
+        <v>2.442012814185546e-08</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0002022338157985359</v>
+        <v>1.97567899817841e-08</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002746710786595941</v>
+        <v>1.267846840846687e-07</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0001248391927219927</v>
+        <v>3.570398376950834e-08</v>
       </c>
       <c r="M16" t="n">
-        <v>0.000517755514010787</v>
+        <v>3.456678143720637e-08</v>
       </c>
       <c r="N16" t="n">
-        <v>0.001340340706519783</v>
+        <v>7.707614457785894e-08</v>
       </c>
       <c r="O16" t="n">
-        <v>0.00029916618950665</v>
+        <v>5.023098026413209e-08</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0008526115561835468</v>
+        <v>4.461114144760359e-09</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0002961884019896388</v>
+        <v>1.240903646504421e-08</v>
       </c>
       <c r="R16" t="n">
-        <v>4.72834790343768e-06</v>
+        <v>9.65515400963568e-09</v>
       </c>
       <c r="S16" t="n">
-        <v>9.301010868512094e-05</v>
+        <v>1.69033209651559e-09</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0006095239077694714</v>
+        <v>3.252220270866246e-09</v>
       </c>
       <c r="U16" t="n">
-        <v>7.098871719790623e-05</v>
+        <v>1.404641292168662e-08</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0003680929366964847</v>
+        <v>1.345690225917906e-09</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0002148073690477759</v>
+        <v>6.406925656676776e-09</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0003272111644037068</v>
+        <v>1.085678569268111e-08</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.745627666125074e-05</v>
+        <v>1.437710572815831e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0008108285837806761</v>
+        <v>1.525574866434454e-08</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0002882797562051564</v>
+        <v>1.639769875438901e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0001253380032721907</v>
+        <v>5.143031334142734e-09</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0003728148876689374</v>
+        <v>1.944967031874967e-08</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0002733762667048723</v>
+        <v>1.453087206115811e-09</v>
       </c>
       <c r="AE16" t="n">
-        <v>8.712828275747597e-05</v>
+        <v>1.812041894311278e-08</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0006566852680407465</v>
+        <v>5.328328889220302e-10</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0002990723005495965</v>
+        <v>4.323773694636657e-08</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.0003046235651709139</v>
+        <v>8.575860022119741e-10</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.692628004297148e-05</v>
+        <v>1.718829167884905e-08</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0001555672497488558</v>
+        <v>2.033968549142173e-08</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0002811766462400556</v>
+        <v>9.79551728619299e-09</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0007178161758929491</v>
+        <v>2.695058043400422e-08</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.0001724655594443902</v>
+        <v>2.625786521548434e-08</v>
       </c>
       <c r="AN16" t="n">
-        <v>8.545386663172394e-05</v>
+        <v>1.329632226543254e-08</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.0001403738715453073</v>
+        <v>4.404122844192671e-09</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0004018415638711303</v>
+        <v>8.31756086228097e-09</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.415245060343295e-05</v>
+        <v>9.966697689378634e-09</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.407879896461964e-05</v>
+        <v>3.973397610934626e-09</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0002101454447256401</v>
+        <v>1.392344683992519e-09</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.0002333652519155294</v>
+        <v>5.269562564080843e-11</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.002666396554559469</v>
+        <v>6.339586633430372e-08</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.0005455538048408926</v>
+        <v>2.372466312294819e-08</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.0003767729504033923</v>
+        <v>2.101800511411511e-09</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.0005961473216302693</v>
+        <v>4.350813753717375e-08</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0001797482254914939</v>
+        <v>4.392153130083898e-08</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.0002583883760962635</v>
+        <v>2.253543351926623e-09</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.094522879924625e-05</v>
+        <v>7.258082135308541e-09</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0001203369756694883</v>
+        <v>5.900021360361052e-09</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.704741488443688e-05</v>
+        <v>1.355251022516768e-09</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.0004612397751770914</v>
+        <v>2.537824528303645e-08</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0003987778327427804</v>
+        <v>9.426420533031887e-09</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.0001437732425983995</v>
+        <v>9.827449964916468e-10</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.0006027529016137123</v>
+        <v>3.687630467652525e-08</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.000103524565929547</v>
+        <v>4.002007170100796e-09</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.0007422186899930239</v>
+        <v>4.640886785978182e-09</v>
       </c>
       <c r="BJ16" t="n">
-        <v>7.345541962422431e-05</v>
+        <v>1.231785962119147e-08</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.0002858482475858182</v>
+        <v>2.223008799262516e-08</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.0002690110413823277</v>
+        <v>7.332128681980521e-09</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0006295129423961043</v>
+        <v>2.673575583145293e-09</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.499058816989418e-05</v>
+        <v>3.549283977832829e-09</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.413142258068547e-05</v>
+        <v>9.731118133515793e-09</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.0005779197090305388</v>
+        <v>3.83374008094961e-08</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.0003689403529278934</v>
+        <v>2.128985876481693e-08</v>
       </c>
       <c r="BR16" t="n">
-        <v>9.512585529591888e-05</v>
+        <v>2.931194398314574e-09</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.000118999058031477</v>
+        <v>7.956725944779919e-09</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.0001369597302982584</v>
+        <v>1.718713527054661e-08</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.000225681607844308</v>
+        <v>1.970958063424177e-09</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.001702003413811326</v>
+        <v>3.220363353761968e-08</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.000506334297824651</v>
+        <v>1.76935106566134e-08</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.0001482142979511991</v>
+        <v>1.388850701111721e-09</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.0001815984578570351</v>
+        <v>1.43019844855985e-08</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0003067503566853702</v>
+        <v>1.947837091620386e-08</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.53424542886205e-05</v>
+        <v>1.847869768312194e-08</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.0001200460756081156</v>
+        <v>1.056891463235843e-09</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.0001595566136529669</v>
+        <v>6.361988713621258e-09</v>
       </c>
       <c r="CD16" t="n">
-        <v>9.273007162846625e-05</v>
+        <v>1.361083512563255e-08</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.0005091717466711998</v>
+        <v>4.046086132802884e-08</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.58793761531706e-06</v>
+        <v>6.426192911135331e-10</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.0001275100512430072</v>
+        <v>1.123487791687694e-08</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.0002222127222921699</v>
+        <v>5.647917689088899e-09</v>
       </c>
       <c r="CI16" t="n">
-        <v>7.726254989393055e-05</v>
+        <v>2.121405984212288e-08</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.65817616309505e-05</v>
+        <v>5.645572898060891e-10</v>
       </c>
       <c r="CK16" t="n">
-        <v>3.596889655455016e-05</v>
+        <v>3.365551393130772e-09</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.0001511993177700788</v>
+        <v>7.647117605813492e-09</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.0007043613586574793</v>
+        <v>1.772235691532842e-10</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0005154233076609671</v>
+        <v>3.866575326583188e-08</v>
       </c>
       <c r="CO16" t="n">
-        <v>3.948250741814263e-05</v>
+        <v>3.343322774185253e-08</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0004154877387918532</v>
+        <v>8.731291245567263e-09</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.001010234816931188</v>
+        <v>2.913944641136368e-08</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.0003072966064792126</v>
+        <v>1.298369767255281e-08</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.000363253871910274</v>
+        <v>1.930287041318479e-08</v>
       </c>
       <c r="CT16" t="n">
-        <v>8.856273780111223e-05</v>
+        <v>2.919970754078349e-08</v>
       </c>
       <c r="CU16" t="n">
-        <v>2.603893517516553e-05</v>
+        <v>1.494352019903999e-08</v>
       </c>
       <c r="CV16" t="n">
-        <v>4.87496581627056e-05</v>
+        <v>9.573073000979093e-09</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.0004164940328337252</v>
+        <v>3.762528066886262e-08</v>
       </c>
       <c r="CX16" t="n">
-        <v>8.427907596342266e-05</v>
+        <v>2.37349251364094e-09</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.0002953385992441326</v>
+        <v>1.281510186856849e-08</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.0001781860482878983</v>
+        <v>8.044766630632694e-09</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.0002121053548762575</v>
+        <v>2.347267269442455e-08</v>
       </c>
       <c r="DB16" t="n">
-        <v>4.575407729134895e-05</v>
+        <v>6.442817390706068e-09</v>
       </c>
       <c r="DC16" t="n">
-        <v>4.090014408575371e-05</v>
+        <v>4.838482947633338e-10</v>
       </c>
       <c r="DD16" t="n">
-        <v>4.917347541777417e-05</v>
+        <v>4.20343093665565e-09</v>
       </c>
       <c r="DE16" t="n">
-        <v>7.723168528173119e-05</v>
+        <v>1.005365568573779e-08</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.0006577661843039095</v>
+        <v>2.123848652502147e-08</v>
       </c>
       <c r="DG16" t="n">
-        <v>9.610445704311132e-05</v>
+        <v>1.432428220482507e-08</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.001233410788699985</v>
+        <v>2.485827543807773e-09</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0005864998092874885</v>
+        <v>1.827460138770221e-08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.0001751945383148268</v>
+        <v>2.727733061647086e-08</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.0003649171558208764</v>
+        <v>3.356125155562495e-09</v>
       </c>
       <c r="DL16" t="n">
-        <v>4.109660949325189e-05</v>
+        <v>1.618579759110617e-08</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.0001392587000736967</v>
+        <v>1.104423663633725e-09</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.0003265844425186515</v>
+        <v>2.738934412604976e-09</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.000215216088690795</v>
+        <v>1.854741071838362e-08</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.0001563797268318012</v>
+        <v>9.961226510313281e-09</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.0001264124002773315</v>
+        <v>1.133218319182561e-08</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.0002385054831393063</v>
+        <v>8.427437414582073e-09</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.000325273402268067</v>
+        <v>1.623690337737571e-08</v>
       </c>
       <c r="DT16" t="n">
-        <v>2.654676791280508e-05</v>
+        <v>1.583190289977665e-08</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.00011196501145605</v>
+        <v>1.507680913448439e-08</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.000217071472434327</v>
+        <v>1.074351985153044e-08</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.0001300642325077206</v>
+        <v>1.399202420593326e-10</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.0001267242041649297</v>
+        <v>1.650428238519908e-08</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.0001375865685986355</v>
+        <v>3.06422087703595e-09</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.0001519230863777921</v>
+        <v>3.483204835674769e-09</v>
       </c>
       <c r="EA16" t="n">
-        <v>2.875209247577004e-05</v>
+        <v>1.221843337617656e-08</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.0001458322367398068</v>
+        <v>3.939222281701404e-09</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.114095306955278e-05</v>
+        <v>3.351461608236406e-10</v>
       </c>
       <c r="ED16" t="n">
-        <v>2.829207005561329e-05</v>
+        <v>3.404911552706835e-08</v>
       </c>
       <c r="EE16" t="n">
-        <v>6.092479452490807e-05</v>
+        <v>1.46537644241107e-08</v>
       </c>
       <c r="EF16" t="n">
-        <v>9.492494427831843e-05</v>
+        <v>1.54302028931852e-08</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0004907465190626681</v>
+        <v>2.158664003104604e-08</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.0001226501917699352</v>
+        <v>3.739146769987656e-10</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.0001269453496206552</v>
+        <v>7.095017018343697e-09</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.0005061262054368854</v>
+        <v>1.88766833275622e-08</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.0001602597476448864</v>
+        <v>2.382843788950595e-08</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.0001096143314498477</v>
+        <v>8.072941426462421e-09</v>
       </c>
       <c r="EM16" t="n">
-        <v>8.521568815922365e-05</v>
+        <v>6.582572265045883e-09</v>
       </c>
       <c r="EN16" t="n">
-        <v>4.0959901525639e-05</v>
+        <v>7.118798883709587e-10</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.0001317830319749191</v>
+        <v>1.276882954925895e-08</v>
       </c>
       <c r="EP16" t="n">
-        <v>4.446371531230398e-05</v>
+        <v>2.257713660469562e-08</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.0004623562272172421</v>
+        <v>1.730830812007866e-09</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.0002970009227283299</v>
+        <v>1.841756747111845e-09</v>
       </c>
       <c r="ES16" t="n">
-        <v>9.202450746670365e-05</v>
+        <v>9.73752456445709e-09</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.0004208787577226758</v>
+        <v>2.803867360512413e-09</v>
       </c>
       <c r="EU16" t="n">
-        <v>4.791388346347958e-05</v>
+        <v>5.200623043322139e-09</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.0004189083119854331</v>
+        <v>8.300856002563251e-09</v>
       </c>
       <c r="EW16" t="n">
-        <v>1.326817891822429e-05</v>
+        <v>7.204983276665189e-10</v>
       </c>
       <c r="EX16" t="n">
-        <v>3.862195808324032e-05</v>
+        <v>1.437286556438266e-08</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.0004216231754980981</v>
+        <v>3.936577996910273e-08</v>
       </c>
       <c r="EZ16" t="n">
-        <v>2.758340087893885e-06</v>
+        <v>3.071576326618697e-09</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.0002054262295132503</v>
+        <v>1.005898120354232e-08</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.0001008200997603126</v>
+        <v>9.661356159540446e-10</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.000130121668917127</v>
+        <v>1.785594427872184e-08</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.0001353046973235905</v>
+        <v>2.84203882650047e-09</v>
       </c>
       <c r="FE16" t="n">
-        <v>4.216031811665744e-05</v>
+        <v>5.302365213566418e-10</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.0001497383345849812</v>
+        <v>8.679932328448103e-10</v>
       </c>
       <c r="FG16" t="n">
-        <v>1.260495719179744e-05</v>
+        <v>6.720494383216646e-09</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.0001764138432918116</v>
+        <v>2.028319912028564e-08</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.0003800145350396633</v>
+        <v>6.665270113614952e-09</v>
       </c>
       <c r="FJ16" t="n">
-        <v>8.476428047288209e-05</v>
+        <v>2.096983031663058e-08</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.0002665062493178993</v>
+        <v>7.685442504623552e-09</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.0001558614167151973</v>
+        <v>2.226534334681673e-08</v>
       </c>
       <c r="FM16" t="n">
-        <v>1.122821231547277e-05</v>
+        <v>3.137188731017204e-09</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.0003731866891030222</v>
+        <v>7.958341541325353e-09</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.0001312490931013599</v>
+        <v>1.014792250231267e-08</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0003102371410932392</v>
+        <v>1.310357689021657e-08</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.0003685947449412197</v>
+        <v>1.159559737118343e-08</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.0004286861221771687</v>
+        <v>4.056977331856615e-08</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.0006709301960654557</v>
+        <v>1.879184807762613e-08</v>
       </c>
       <c r="FT16" t="n">
-        <v>1.115212944569066e-05</v>
+        <v>2.256582476434232e-08</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.0001820102625060827</v>
+        <v>2.782519992194921e-09</v>
       </c>
       <c r="FV16" t="n">
-        <v>0.0002417466603219509</v>
+        <v>1.243220193458683e-09</v>
       </c>
       <c r="FW16" t="n">
-        <v>5.306618550093845e-05</v>
+        <v>1.938032134773948e-08</v>
       </c>
       <c r="FX16" t="n">
-        <v>4.368409281596541e-05</v>
+        <v>1.916779268640312e-08</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.0004225873854011297</v>
+        <v>1.460609944103908e-08</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.0002800350484903902</v>
+        <v>4.874359582629495e-09</v>
       </c>
       <c r="GA16" t="n">
-        <v>4.322220411268063e-05</v>
+        <v>1.406161409533979e-08</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.0001040885545080528</v>
+        <v>3.011320526269401e-09</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.0004813828272745013</v>
+        <v>8.122365890983474e-09</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.0004349676601123065</v>
+        <v>2.465049497857308e-08</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0008778938790783286</v>
+        <v>1.196451204776849e-08</v>
       </c>
       <c r="GF16" t="n">
-        <v>7.670375634916127e-05</v>
+        <v>3.861034603147573e-09</v>
       </c>
       <c r="GG16" t="n">
-        <v>7.366538920905441e-05</v>
+        <v>1.262351911890391e-08</v>
       </c>
     </row>
   </sheetData>
